--- a/datadelevry_clean_preview(200lignes).xlsx
+++ b/datadelevry_clean_preview(200lignes).xlsx
@@ -502,19 +502,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-1.280868457362067</v>
+        <v>-1.315717598106123</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1508047456973569</v>
+        <v>0.9100999367494796</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.023149403824343</v>
+        <v>-0.0836455322957689</v>
       </c>
       <c r="D2" t="n">
         <v>-1.20517484870554</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3016562502268909</v>
+        <v>0.3016562502268911</v>
       </c>
       <c r="F2" t="n">
         <v>0.4185914320397559</v>
@@ -535,7 +535,7 @@
         <v>1.580513718626727</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4093091191273296</v>
+        <v>0.4005617817073991</v>
       </c>
       <c r="M2" t="n">
         <v>0.7037713167782218</v>
@@ -546,19 +546,19 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-0.7681065740310408</v>
+        <v>-0.6520228310981192</v>
       </c>
       <c r="B3" t="n">
-        <v>0.1994267014020912</v>
+        <v>1.15689502067604</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.459139787003341</v>
+        <v>0.2995775852002966</v>
       </c>
       <c r="D3" t="n">
         <v>-0.5372365216588224</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.8317401748482529</v>
+        <v>-0.831740174848253</v>
       </c>
       <c r="F3" t="n">
         <v>-0.4341230922645889</v>
@@ -579,7 +579,7 @@
         <v>1.46388827866443</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.9368993718770108</v>
+        <v>-0.9168831095825996</v>
       </c>
       <c r="M3" t="n">
         <v>0.7037713167782218</v>
@@ -590,19 +590,19 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1994267014020912</v>
+        <v>1.15689502067604</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.023149403824343</v>
+        <v>-0.0836455322957689</v>
       </c>
       <c r="D4" t="n">
         <v>-1.20517484870554</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.8317401748482529</v>
+        <v>-0.831740174848253</v>
       </c>
       <c r="F4" t="n">
         <v>-0.4341230922645889</v>
@@ -623,7 +623,7 @@
         <v>1.347262838702132</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.9368993718770108</v>
+        <v>-0.9168831095825996</v>
       </c>
       <c r="M4" t="n">
         <v>1.055556285591372</v>
@@ -634,13 +634,13 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1994267014020912</v>
+        <v>1.15689502067604</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.023149403824343</v>
+        <v>-0.0836455322957689</v>
       </c>
       <c r="D5" t="n">
         <v>-1.20517484870554</v>
@@ -667,7 +667,7 @@
         <v>1.46388827866443</v>
       </c>
       <c r="L5" t="n">
-        <v>1.431795920212737</v>
+        <v>1.401201743127076</v>
       </c>
       <c r="M5" t="n">
         <v>1.055556285591372</v>
@@ -678,13 +678,13 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1994267014020912</v>
+        <v>1.15689502067604</v>
       </c>
       <c r="C6" t="n">
-        <v>-1.023149403824343</v>
+        <v>-0.0836455322957689</v>
       </c>
       <c r="D6" t="n">
         <v>-1.20517484870554</v>
@@ -711,7 +711,7 @@
         <v>-0.7519950806192256</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.122039488682346e-16</v>
+        <v>0.8516166460297001</v>
       </c>
       <c r="M6" t="n">
         <v>-1.406938496100678</v>
@@ -722,13 +722,13 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1994267014020912</v>
+        <v>1.15689502067604</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.023149403824343</v>
+        <v>-0.0836455322957689</v>
       </c>
       <c r="D7" t="n">
         <v>-1.20517484870554</v>
@@ -755,7 +755,7 @@
         <v>1.347262838702132</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1473342745137612</v>
+        <v>-0.1441881586793745</v>
       </c>
       <c r="M7" t="n">
         <v>0.7037713167782218</v>
@@ -766,19 +766,19 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1994267014020912</v>
+        <v>1.15689502067604</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.023149403824343</v>
+        <v>-0.0836455322957689</v>
       </c>
       <c r="D8" t="n">
         <v>-1.20517484870554</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F8" t="n">
         <v>0.6725797296748594</v>
@@ -799,7 +799,7 @@
         <v>-0.7519950806192256</v>
       </c>
       <c r="L8" t="n">
-        <v>2.023969743235175</v>
+        <v>1.980722956304494</v>
       </c>
       <c r="M8" t="n">
         <v>-1.406938496100678</v>
@@ -810,19 +810,19 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B9" t="n">
-        <v>0.1994267014020912</v>
+        <v>1.15689502067604</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.023149403824343</v>
+        <v>-0.0836455322957689</v>
       </c>
       <c r="D9" t="n">
         <v>-1.20517484870554</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3016562502268909</v>
+        <v>0.3016562502268911</v>
       </c>
       <c r="F9" t="n">
         <v>1.198263570096097</v>
@@ -843,7 +843,7 @@
         <v>-0.6353696406569279</v>
       </c>
       <c r="L9" t="n">
-        <v>1.135709008701519</v>
+        <v>1.111441136538366</v>
       </c>
       <c r="M9" t="n">
         <v>0.7037713167782218</v>
@@ -854,19 +854,19 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-0.7681065740310408</v>
+        <v>-0.6520228310981192</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1994267014020912</v>
+        <v>1.15689502067604</v>
       </c>
       <c r="C10" t="n">
-        <v>-1.417956135599045</v>
+        <v>-0.3573763305072443</v>
       </c>
       <c r="D10" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3016562502268909</v>
+        <v>0.3016562502268911</v>
       </c>
       <c r="F10" t="n">
         <v>1.154548808629489</v>
@@ -887,7 +887,7 @@
         <v>-0.9852459605438209</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6106482189549582</v>
+        <v>0.5975989941877216</v>
       </c>
       <c r="M10" t="n">
         <v>0.7037713167782218</v>
@@ -898,19 +898,19 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B11" t="n">
-        <v>0.1994267014020912</v>
+        <v>1.15689502067604</v>
       </c>
       <c r="C11" t="n">
-        <v>-1.023149403824343</v>
+        <v>-0.0836455322957689</v>
       </c>
       <c r="D11" t="n">
         <v>-1.20517484870554</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F11" t="n">
         <v>-0.3234528100706441</v>
@@ -931,7 +931,7 @@
         <v>-0.8686205205815232</v>
       </c>
       <c r="L11" t="n">
-        <v>0.050056999827051</v>
+        <v>0.0489855790464317</v>
       </c>
       <c r="M11" t="n">
         <v>-1.406938496100678</v>
@@ -942,19 +942,19 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B12" t="n">
-        <v>0.1994267014020912</v>
+        <v>1.15689502067604</v>
       </c>
       <c r="C12" t="n">
-        <v>-1.023149403824343</v>
+        <v>-0.0836455322957689</v>
       </c>
       <c r="D12" t="n">
         <v>0.7986401324346124</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3016562502268909</v>
+        <v>0.3016562502268911</v>
       </c>
       <c r="F12" t="n">
         <v>0.893920294062749</v>
@@ -975,7 +975,7 @@
         <v>1.230637398739834</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.3447255488545736</v>
+        <v>-0.3373618964051808</v>
       </c>
       <c r="M12" t="n">
         <v>0.7037713167782218</v>
@@ -986,19 +986,19 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B13" t="n">
-        <v>0.1994267014020912</v>
+        <v>1.15689502067604</v>
       </c>
       <c r="C13" t="n">
-        <v>-1.023149403824343</v>
+        <v>-0.0836455322957689</v>
       </c>
       <c r="D13" t="n">
         <v>-1.20517484870554</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.167866258961605e-17</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
         <v>-0.2681176689736717</v>
@@ -1010,7 +1010,7 @@
         <v>-1.081392643376533</v>
       </c>
       <c r="I13" t="n">
-        <v>48.65323800593746</v>
+        <v>50.64185337217514</v>
       </c>
       <c r="J13" t="n">
         <v>-1.589382247207237</v>
@@ -1019,7 +1019,7 @@
         <v>-0.5187442006946303</v>
       </c>
       <c r="L13" t="n">
-        <v>1.037013371531113</v>
+        <v>1.014854267675463</v>
       </c>
       <c r="M13" t="n">
         <v>-1.406938496100678</v>
@@ -1030,19 +1030,19 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B14" t="n">
-        <v>0.1994267014020912</v>
+        <v>1.15689502067604</v>
       </c>
       <c r="C14" t="n">
-        <v>-1.023149403824343</v>
+        <v>-0.0836455322957689</v>
       </c>
       <c r="D14" t="n">
         <v>-1.20517484870554</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.8317401748482529</v>
+        <v>-0.831740174848253</v>
       </c>
       <c r="F14" t="n">
         <v>-0.4341230922645889</v>
@@ -1063,7 +1063,7 @@
         <v>-0.8686205205815232</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.9368993718770108</v>
+        <v>-0.9168831095825996</v>
       </c>
       <c r="M14" t="n">
         <v>0.7037713167782218</v>
@@ -1074,19 +1074,19 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B15" t="n">
-        <v>0.1994267014020912</v>
+        <v>1.15689502067604</v>
       </c>
       <c r="C15" t="n">
-        <v>-1.023149403824343</v>
+        <v>-0.0836455322957689</v>
       </c>
       <c r="D15" t="n">
         <v>0.7986401324346124</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3016562502268909</v>
+        <v>0.3016562502268911</v>
       </c>
       <c r="F15" t="n">
         <v>1.27351936198798</v>
@@ -1107,7 +1107,7 @@
         <v>-0.8686205205815232</v>
       </c>
       <c r="L15" t="n">
-        <v>2.345717520410699</v>
+        <v>2.295596148797558</v>
       </c>
       <c r="M15" t="n">
         <v>0.7037713167782218</v>
@@ -1118,19 +1118,19 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>-1.280868457362067</v>
+        <v>-1.315717598106123</v>
       </c>
       <c r="B16" t="n">
-        <v>0.169990439124436</v>
+        <v>1.135459766907771</v>
       </c>
       <c r="C16" t="n">
-        <v>-1.192352288870644</v>
+        <v>-0.1931378515803591</v>
       </c>
       <c r="D16" t="n">
         <v>-1.20517484870554</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.8317401748482529</v>
+        <v>-0.831740174848253</v>
       </c>
       <c r="F16" t="n">
         <v>-0.6416298713782355</v>
@@ -1151,7 +1151,7 @@
         <v>-0.6353696406569279</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.9368993718770108</v>
+        <v>-0.9168831095825996</v>
       </c>
       <c r="M16" t="n">
         <v>-1.406938496100678</v>
@@ -1162,19 +1162,19 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>-1.280868457362067</v>
+        <v>-1.315717598106123</v>
       </c>
       <c r="B17" t="n">
-        <v>0.169990439124436</v>
+        <v>1.135459766907771</v>
       </c>
       <c r="C17" t="n">
-        <v>-1.192352288870644</v>
+        <v>-0.1931378515803591</v>
       </c>
       <c r="D17" t="n">
         <v>-1.20517484870554</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F17" t="n">
         <v>0.5176413346033365</v>
@@ -1195,7 +1195,7 @@
         <v>-0.7519950806192256</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5830134405472445</v>
+        <v>0.5705546709061087</v>
       </c>
       <c r="M17" t="n">
         <v>1.055556285591372</v>
@@ -1206,13 +1206,13 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>-1.280868457362067</v>
+        <v>-1.315717598106123</v>
       </c>
       <c r="B18" t="n">
-        <v>0.169990439124436</v>
+        <v>1.135459766907771</v>
       </c>
       <c r="C18" t="n">
-        <v>-1.192352288870644</v>
+        <v>-0.1931378515803591</v>
       </c>
       <c r="D18" t="n">
         <v>-1.20517484870554</v>
@@ -1230,7 +1230,7 @@
         <v>-1.141369801869188</v>
       </c>
       <c r="I18" t="n">
-        <v>46.66646479858689</v>
+        <v>47.05872142809851</v>
       </c>
       <c r="J18" t="n">
         <v>0.3854180897153589</v>
@@ -1239,7 +1239,7 @@
         <v>-0.9852459605438209</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8396220971903006</v>
+        <v>0.8216805299496568</v>
       </c>
       <c r="M18" t="n">
         <v>0.7037713167782218</v>
@@ -1250,13 +1250,13 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>-1.280868457362067</v>
+        <v>-1.315717598106123</v>
       </c>
       <c r="B19" t="n">
-        <v>0.169990439124436</v>
+        <v>1.135459766907771</v>
       </c>
       <c r="C19" t="n">
-        <v>-1.192352288870644</v>
+        <v>-0.1931378515803591</v>
       </c>
       <c r="D19" t="n">
         <v>-1.20517484870554</v>
@@ -1274,7 +1274,7 @@
         <v>-1.101385029540751</v>
       </c>
       <c r="I19" t="n">
-        <v>45.53478803851625</v>
+        <v>45.94665749950344</v>
       </c>
       <c r="J19" t="n">
         <v>1.372818258176657</v>
@@ -1283,7 +1283,7 @@
         <v>-0.7519950806192256</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.3447255488545736</v>
+        <v>-0.3373618964051808</v>
       </c>
       <c r="M19" t="n">
         <v>0.7037713167782218</v>
@@ -1294,19 +1294,19 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>-1.280868457362067</v>
+        <v>-1.315717598106123</v>
       </c>
       <c r="B20" t="n">
-        <v>0.169990439124436</v>
+        <v>1.135459766907771</v>
       </c>
       <c r="C20" t="n">
-        <v>-1.192352288870644</v>
+        <v>-0.1931378515803591</v>
       </c>
       <c r="D20" t="n">
         <v>-1.20517484870554</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F20" t="n">
         <v>0.2575661714475662</v>
@@ -1327,7 +1327,7 @@
         <v>-2.071683979250907e-16</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.122039488682346e-16</v>
+        <v>1.093083818186958</v>
       </c>
       <c r="M20" t="n">
         <v>-1.758723464913828</v>
@@ -1338,19 +1338,19 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>-1.280868457362067</v>
+        <v>-1.315717598106123</v>
       </c>
       <c r="B21" t="n">
-        <v>-0.4998347127038395</v>
+        <v>0.6644635151887719</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.459139787003341</v>
+        <v>0.2995775852002966</v>
       </c>
       <c r="D21" t="n">
         <v>-1.20517484870554</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F21" t="n">
         <v>-0.9598069326858268</v>
@@ -1371,7 +1371,7 @@
         <v>-0.7519950806192256</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1487526369974572</v>
+        <v>0.1455724479093348</v>
       </c>
       <c r="M21" t="n">
         <v>-1.406938496100678</v>
@@ -1382,19 +1382,19 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>-1.280868457362067</v>
+        <v>-1.315717598106123</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.4998347127038395</v>
+        <v>0.6644635151887719</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.459139787003341</v>
+        <v>0.2995775852002966</v>
       </c>
       <c r="D22" t="n">
         <v>-1.20517484870554</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6794550585852722</v>
+        <v>0.6794550585852724</v>
       </c>
       <c r="F22" t="n">
         <v>-0.7744342100109692</v>
@@ -1415,7 +1415,7 @@
         <v>1.697139158589025</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.4434211860249798</v>
+        <v>-0.4339487652680839</v>
       </c>
       <c r="M22" t="n">
         <v>-1.406938496100678</v>
@@ -1426,19 +1426,19 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>-1.280868457362067</v>
+        <v>-1.315717598106123</v>
       </c>
       <c r="B23" t="n">
-        <v>0.0246113478756085</v>
+        <v>1.034076809895686</v>
       </c>
       <c r="C23" t="n">
-        <v>-1.192352288870644</v>
+        <v>-0.1931378515803591</v>
       </c>
       <c r="D23" t="n">
         <v>-1.20517484870554</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3016562502268909</v>
+        <v>0.3016562502268911</v>
       </c>
       <c r="F23" t="n">
         <v>1.723947410517335</v>
@@ -1459,7 +1459,7 @@
         <v>-0.6353696406569279</v>
       </c>
       <c r="L23" t="n">
-        <v>1.62918719455355</v>
+        <v>1.594375480852882</v>
       </c>
       <c r="M23" t="n">
         <v>1.055556285591372</v>
@@ -1470,19 +1470,19 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>-1.280868457362067</v>
+        <v>-1.315717598106123</v>
       </c>
       <c r="B24" t="n">
-        <v>0.0246113478756085</v>
+        <v>1.034076809895686</v>
       </c>
       <c r="C24" t="n">
-        <v>-1.192352288870644</v>
+        <v>-0.1931378515803591</v>
       </c>
       <c r="D24" t="n">
         <v>-1.20517484870554</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F24" t="n">
         <v>0.06389317760816279</v>
@@ -1503,7 +1503,7 @@
         <v>-0.8686205205815232</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.1473342745137612</v>
+        <v>-0.1441881586793745</v>
       </c>
       <c r="M24" t="n">
         <v>-1.406938496100678</v>
@@ -1514,13 +1514,13 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>-1.280868457362067</v>
+        <v>-1.315717598106123</v>
       </c>
       <c r="B25" t="n">
-        <v>0.0246113478756085</v>
+        <v>1.034076809895686</v>
       </c>
       <c r="C25" t="n">
-        <v>-1.192352288870644</v>
+        <v>-0.1931378515803591</v>
       </c>
       <c r="D25" t="n">
         <v>-1.20517484870554</v>
@@ -1538,7 +1538,7 @@
         <v>-0.9414459402270036</v>
       </c>
       <c r="I25" t="n">
-        <v>48.65295652047818</v>
+        <v>52.3860200388418</v>
       </c>
       <c r="J25" t="n">
         <v>-1.589382247207237</v>
@@ -1547,7 +1547,7 @@
         <v>-0.4021187607323326</v>
       </c>
       <c r="L25" t="n">
-        <v>4.392665035324924</v>
+        <v>4.298807809014169</v>
       </c>
       <c r="M25" t="n">
         <v>-1.406938496100678</v>
@@ -1558,13 +1558,13 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>-1.280868457362067</v>
+        <v>-1.315717598106123</v>
       </c>
       <c r="B26" t="n">
-        <v>0.0246113478756085</v>
+        <v>1.034076809895686</v>
       </c>
       <c r="C26" t="n">
-        <v>-1.023149403824343</v>
+        <v>-0.0836455322957689</v>
       </c>
       <c r="D26" t="n">
         <v>-1.20517484870554</v>
@@ -1582,7 +1582,7 @@
         <v>-0.3816591276288876</v>
       </c>
       <c r="I26" t="n">
-        <v>48.65270066848628</v>
+        <v>50.77615437411723</v>
       </c>
       <c r="J26" t="n">
         <v>-1.589382247207237</v>
@@ -1591,7 +1591,7 @@
         <v>-0.7519950806192256</v>
       </c>
       <c r="L26" t="n">
-        <v>0.4448395485086758</v>
+        <v>0.4353330544980442</v>
       </c>
       <c r="M26" t="n">
         <v>-1.406938496100678</v>
@@ -1602,13 +1602,13 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>-1.280868457362067</v>
+        <v>-1.315717598106123</v>
       </c>
       <c r="B27" t="n">
-        <v>0.0246113478756085</v>
+        <v>1.034076809895686</v>
       </c>
       <c r="C27" t="n">
-        <v>-1.192352288870644</v>
+        <v>-0.1931378515803591</v>
       </c>
       <c r="D27" t="n">
         <v>-1.20517484870554</v>
@@ -1635,7 +1635,7 @@
         <v>-0.8686205205815232</v>
       </c>
       <c r="L27" t="n">
-        <v>-1.122039488682346e-16</v>
+        <v>-0.0299361160800435</v>
       </c>
       <c r="M27" t="n">
         <v>-1.406938496100678</v>
@@ -1646,19 +1646,19 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>-1.280868457362067</v>
+        <v>-1.315717598106123</v>
       </c>
       <c r="B28" t="n">
-        <v>0.0246113478756085</v>
+        <v>1.034076809895686</v>
       </c>
       <c r="C28" t="n">
-        <v>-1.192352288870644</v>
+        <v>-0.1931378515803591</v>
       </c>
       <c r="D28" t="n">
         <v>-1.20517484870554</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.8317401748482529</v>
+        <v>-0.831740174848253</v>
       </c>
       <c r="F28" t="n">
         <v>-0.4894582333615613</v>
@@ -1679,7 +1679,7 @@
         <v>-0.7519950806192256</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.9368993718770108</v>
+        <v>-0.9168831095825996</v>
       </c>
       <c r="M28" t="n">
         <v>0.7037713167782218</v>
@@ -1690,19 +1690,19 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>-1.280868457362067</v>
+        <v>-1.315717598106123</v>
       </c>
       <c r="B29" t="n">
-        <v>0.0246113478756085</v>
+        <v>1.034076809895686</v>
       </c>
       <c r="C29" t="n">
-        <v>-1.192352288870644</v>
+        <v>-0.1931378515803591</v>
       </c>
       <c r="D29" t="n">
         <v>-1.20517484870554</v>
       </c>
       <c r="E29" t="n">
-        <v>0.3016562502268909</v>
+        <v>0.3016562502268911</v>
       </c>
       <c r="F29" t="n">
         <v>1.723947410517335</v>
@@ -1723,7 +1723,7 @@
         <v>-0.5187442006946303</v>
       </c>
       <c r="L29" t="n">
-        <v>1.62918719455355</v>
+        <v>1.594375480852882</v>
       </c>
       <c r="M29" t="n">
         <v>-1.406938496100678</v>
@@ -1734,13 +1734,13 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>-1.280868457362067</v>
+        <v>-1.315717598106123</v>
       </c>
       <c r="B30" t="n">
-        <v>0.0246113478756085</v>
+        <v>1.034076809895686</v>
       </c>
       <c r="C30" t="n">
-        <v>-1.192352288870644</v>
+        <v>-0.1931378515803591</v>
       </c>
       <c r="D30" t="n">
         <v>-1.20517484870554</v>
@@ -1767,7 +1767,7 @@
         <v>-0.7519950806192256</v>
       </c>
       <c r="L30" t="n">
-        <v>1.037013371531113</v>
+        <v>1.014854267675463</v>
       </c>
       <c r="M30" t="n">
         <v>0.7037713167782218</v>
@@ -1778,19 +1778,19 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>-1.280868457362067</v>
+        <v>-1.315717598106123</v>
       </c>
       <c r="B31" t="n">
-        <v>0.0246113478756085</v>
+        <v>1.034076809895686</v>
       </c>
       <c r="C31" t="n">
-        <v>-1.192352288870644</v>
+        <v>-0.1931378515803591</v>
       </c>
       <c r="D31" t="n">
         <v>-1.20517484870554</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.8317401748482529</v>
+        <v>-0.831740174848253</v>
       </c>
       <c r="F31" t="n">
         <v>-0.4894582333615613</v>
@@ -1811,7 +1811,7 @@
         <v>-0.8686205205815232</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.9368993718770108</v>
+        <v>-0.9168831095825996</v>
       </c>
       <c r="M31" t="n">
         <v>1.055556285591372</v>
@@ -1822,19 +1822,19 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>-1.280868457362067</v>
+        <v>-1.315717598106123</v>
       </c>
       <c r="B32" t="n">
-        <v>0.0246113478756085</v>
+        <v>1.034076809895686</v>
       </c>
       <c r="C32" t="n">
-        <v>-1.192352288870644</v>
+        <v>-0.1931378515803591</v>
       </c>
       <c r="D32" t="n">
         <v>-1.20517484870554</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F32" t="n">
         <v>0.0085580365111903</v>
@@ -1855,7 +1855,7 @@
         <v>-0.8686205205815232</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.3447255488545736</v>
+        <v>-0.3373618964051808</v>
       </c>
       <c r="M32" t="n">
         <v>-1.406938496100678</v>
@@ -1866,19 +1866,19 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B33" t="n">
-        <v>-1.473033588005908</v>
+        <v>-1.206776205662847</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4996765615923628</v>
+        <v>1.011277660550133</v>
       </c>
       <c r="D33" t="n">
         <v>-0.5372365216588224</v>
       </c>
       <c r="E33" t="n">
-        <v>0.3016562502268909</v>
+        <v>0.3016562502268911</v>
       </c>
       <c r="F33" t="n">
         <v>0.4457056511772724</v>
@@ -1899,7 +1899,7 @@
         <v>1.230637398739834</v>
       </c>
       <c r="L33" t="n">
-        <v>0.3954917299234727</v>
+        <v>0.3870396200665927</v>
       </c>
       <c r="M33" t="n">
         <v>0.7037713167782218</v>
@@ -1910,13 +1910,13 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>-1.280868457362067</v>
+        <v>-1.315717598106123</v>
       </c>
       <c r="B34" t="n">
-        <v>-1.473033588005908</v>
+        <v>-1.206776205662847</v>
       </c>
       <c r="C34" t="n">
-        <v>-1.023149403824343</v>
+        <v>-0.0836455322957689</v>
       </c>
       <c r="D34" t="n">
         <v>-1.20517484870554</v>
@@ -1943,7 +1943,7 @@
         <v>1.347262838702132</v>
       </c>
       <c r="L34" t="n">
-        <v>0.2869265290360259</v>
+        <v>0.2807940643173993</v>
       </c>
       <c r="M34" t="n">
         <v>-1.406938496100678</v>
@@ -1954,19 +1954,19 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>-1.280868457362067</v>
+        <v>-1.315717598106123</v>
       </c>
       <c r="B35" t="n">
-        <v>-1.473033588005908</v>
+        <v>-1.206776205662847</v>
       </c>
       <c r="C35" t="n">
-        <v>-1.023149403824343</v>
+        <v>-0.0836455322957689</v>
       </c>
       <c r="D35" t="n">
         <v>-0.5372365216588224</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.8317401748482529</v>
+        <v>-0.831740174848253</v>
       </c>
       <c r="F35" t="n">
         <v>-0.9459731474115836</v>
@@ -1987,7 +1987,7 @@
         <v>1.347262838702132</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.9368993718770108</v>
+        <v>-0.9168831095825996</v>
       </c>
       <c r="M35" t="n">
         <v>-1.406938496100678</v>
@@ -1998,13 +1998,13 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>-1.280868457362067</v>
+        <v>-1.315717598106123</v>
       </c>
       <c r="B36" t="n">
-        <v>-1.473033588005908</v>
+        <v>-1.206776205662847</v>
       </c>
       <c r="C36" t="n">
-        <v>-1.023149403824343</v>
+        <v>-0.0836455322957689</v>
       </c>
       <c r="D36" t="n">
         <v>-0.5372365216588224</v>
@@ -2031,7 +2031,7 @@
         <v>1.46388827866443</v>
       </c>
       <c r="L36" t="n">
-        <v>0.4941873670938789</v>
+        <v>0.4836264889294958</v>
       </c>
       <c r="M36" t="n">
         <v>-1.406938496100678</v>
@@ -2042,19 +2042,19 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>-0.7681065740310408</v>
+        <v>-0.6520228310981192</v>
       </c>
       <c r="B37" t="n">
-        <v>-1.473033588005908</v>
+        <v>-1.206776205662847</v>
       </c>
       <c r="C37" t="n">
-        <v>1.289290025141766</v>
+        <v>1.613485416615379</v>
       </c>
       <c r="D37" t="n">
         <v>1.46657845948133</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.8317401748482529</v>
+        <v>-0.831740174848253</v>
       </c>
       <c r="F37" t="n">
         <v>-0.8104020517240013</v>
@@ -2075,7 +2075,7 @@
         <v>1.347262838702132</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.9368993718770108</v>
+        <v>-0.9168831095825996</v>
       </c>
       <c r="M37" t="n">
         <v>-1.406938496100678</v>
@@ -2086,19 +2086,19 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>-1.280868457362067</v>
+        <v>-1.315717598106123</v>
       </c>
       <c r="B38" t="n">
-        <v>-1.473033588005908</v>
+        <v>-1.206776205662847</v>
       </c>
       <c r="C38" t="n">
-        <v>-1.023149403824343</v>
+        <v>-0.0836455322957689</v>
       </c>
       <c r="D38" t="n">
         <v>-0.5372365216588224</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F38" t="n">
         <v>-0.5171258039100475</v>
@@ -2119,7 +2119,7 @@
         <v>1.347262838702132</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.9368993718770108</v>
+        <v>-0.9168831095825996</v>
       </c>
       <c r="M38" t="n">
         <v>0.7037713167782218</v>
@@ -2130,19 +2130,19 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>-1.280868457362067</v>
+        <v>-1.315717598106123</v>
       </c>
       <c r="B39" t="n">
-        <v>-1.473033588005908</v>
+        <v>-1.206776205662847</v>
       </c>
       <c r="C39" t="n">
-        <v>-1.023149403824343</v>
+        <v>-0.0836455322957689</v>
       </c>
       <c r="D39" t="n">
         <v>-0.5372365216588224</v>
       </c>
       <c r="E39" t="n">
-        <v>1.812851483660416</v>
+        <v>1.812851483660417</v>
       </c>
       <c r="F39" t="n">
         <v>-2.516350882477691e-16</v>
@@ -2163,7 +2163,7 @@
         <v>1.230637398739834</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.7987254798384421</v>
+        <v>-0.7816614931745351</v>
       </c>
       <c r="M39" t="n">
         <v>-1.406938496100678</v>
@@ -2174,19 +2174,19 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>-1.280868457362067</v>
+        <v>-1.315717598106123</v>
       </c>
       <c r="B40" t="n">
-        <v>-1.473033588005908</v>
+        <v>-1.206776205662847</v>
       </c>
       <c r="C40" t="n">
-        <v>-1.023149403824343</v>
+        <v>-0.0836455322957689</v>
       </c>
       <c r="D40" t="n">
         <v>-0.5372365216588224</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F40" t="n">
         <v>-0.5309595891842906</v>
@@ -2207,7 +2207,7 @@
         <v>1.347262838702132</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.7888559161214015</v>
+        <v>-0.7720028062882448</v>
       </c>
       <c r="M40" t="n">
         <v>1.055556285591372</v>
@@ -2218,13 +2218,13 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>-1.280868457362067</v>
+        <v>-1.315717598106123</v>
       </c>
       <c r="B41" t="n">
-        <v>-1.473033588005908</v>
+        <v>-1.206776205662847</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.023149403824343</v>
+        <v>-0.0836455322957689</v>
       </c>
       <c r="D41" t="n">
         <v>-0.5372365216588224</v>
@@ -2251,7 +2251,7 @@
         <v>1.347262838702132</v>
       </c>
       <c r="L41" t="n">
-        <v>0.3066656564701072</v>
+        <v>0.3001114380899798</v>
       </c>
       <c r="M41" t="n">
         <v>0.7037713167782218</v>
@@ -2262,19 +2262,19 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>-1.280868457362067</v>
+        <v>-1.315717598106123</v>
       </c>
       <c r="B42" t="n">
-        <v>-1.473033588005908</v>
+        <v>-1.206776205662847</v>
       </c>
       <c r="C42" t="n">
-        <v>-1.023149403824343</v>
+        <v>-0.0836455322957689</v>
       </c>
       <c r="D42" t="n">
         <v>-0.5372365216588224</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.8317401748482529</v>
+        <v>-0.831740174848253</v>
       </c>
       <c r="F42" t="n">
         <v>-0.8104020517240013</v>
@@ -2295,7 +2295,7 @@
         <v>1.347262838702132</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.9368993718770108</v>
+        <v>-0.9168831095825996</v>
       </c>
       <c r="M42" t="n">
         <v>-1.406938496100678</v>
@@ -2306,19 +2306,19 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>-1.280868457362067</v>
+        <v>-1.315717598106123</v>
       </c>
       <c r="B43" t="n">
-        <v>0.5778929306862289</v>
+        <v>1.422808033639165</v>
       </c>
       <c r="C43" t="n">
-        <v>1.627695795234367</v>
+        <v>-1.561791842637736</v>
       </c>
       <c r="D43" t="n">
         <v>0.7986401324346124</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F43" t="n">
         <v>-1.156246683580079</v>
@@ -2339,7 +2339,7 @@
         <v>1.114011958777537</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.749377661253239</v>
+        <v>-0.7333680587430836</v>
       </c>
       <c r="M43" t="n">
         <v>1.055556285591372</v>
@@ -2350,19 +2350,19 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B44" t="n">
-        <v>0.0612564907110567</v>
+        <v>1.059567381944439</v>
       </c>
       <c r="C44" t="n">
-        <v>-1.192352288870644</v>
+        <v>-0.1931378515803591</v>
       </c>
       <c r="D44" t="n">
         <v>-1.20517484870554</v>
       </c>
       <c r="E44" t="n">
-        <v>0.3016562502268909</v>
+        <v>0.3016562502268911</v>
       </c>
       <c r="F44" t="n">
         <v>1.557941987226418</v>
@@ -2383,7 +2383,7 @@
         <v>-0.8686205205815232</v>
       </c>
       <c r="L44" t="n">
-        <v>1.431795920212737</v>
+        <v>1.401201743127076</v>
       </c>
       <c r="M44" t="n">
         <v>0.7037713167782218</v>
@@ -2394,19 +2394,19 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B45" t="n">
-        <v>-0.3808881835002534</v>
+        <v>0.7484665367130705</v>
       </c>
       <c r="C45" t="n">
-        <v>-1.192352288870644</v>
+        <v>-0.1931378515803591</v>
       </c>
       <c r="D45" t="n">
         <v>-1.20517484870554</v>
       </c>
       <c r="E45" t="n">
-        <v>0.6794550585852722</v>
+        <v>0.6794550585852724</v>
       </c>
       <c r="F45" t="n">
         <v>1.502606846129446</v>
@@ -2418,7 +2418,7 @@
         <v>3.436886629736832</v>
       </c>
       <c r="I45" t="n">
-        <v>45.06083333333333</v>
+        <v>81.3</v>
       </c>
       <c r="J45" t="n">
         <v>0.879118173946008</v>
@@ -2427,7 +2427,7 @@
         <v>-0.6353696406569279</v>
       </c>
       <c r="L45" t="n">
-        <v>2.221361017575988</v>
+        <v>2.1738966940303</v>
       </c>
       <c r="M45" t="n">
         <v>1.055556285591372</v>
@@ -2438,19 +2438,19 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B46" t="n">
-        <v>0.0612564907110567</v>
+        <v>1.059567381944439</v>
       </c>
       <c r="C46" t="n">
-        <v>-1.192352288870644</v>
+        <v>-0.1931378515803591</v>
       </c>
       <c r="D46" t="n">
         <v>-1.20517484870554</v>
       </c>
       <c r="E46" t="n">
-        <v>0.3016562502268909</v>
+        <v>0.3016562502268911</v>
       </c>
       <c r="F46" t="n">
         <v>2.445517650421855</v>
@@ -2471,7 +2471,7 @@
         <v>-0.7519950806192256</v>
       </c>
       <c r="L46" t="n">
-        <v>1.905534978630688</v>
+        <v>1.86481871366901</v>
       </c>
       <c r="M46" t="n">
         <v>0.7037713167782218</v>
@@ -2482,19 +2482,19 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>-0.2553446907000148</v>
+        <v>-2.947396846622059e-16</v>
       </c>
       <c r="B47" t="n">
-        <v>0.0612564907110567</v>
+        <v>1.059567381944439</v>
       </c>
       <c r="C47" t="n">
-        <v>-1.192352288870644</v>
+        <v>-0.1931378515803591</v>
       </c>
       <c r="D47" t="n">
         <v>-1.20517484870554</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F47" t="n">
         <v>-0.1574473867797268</v>
@@ -2515,7 +2515,7 @@
         <v>-0.6353696406569279</v>
       </c>
       <c r="L47" t="n">
-        <v>1.431795920212737</v>
+        <v>1.401201743127076</v>
       </c>
       <c r="M47" t="n">
         <v>-1.758723464913828</v>
@@ -2526,19 +2526,19 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B48" t="n">
-        <v>1.193050738284573</v>
+        <v>-1.235742764809157</v>
       </c>
       <c r="C48" t="n">
-        <v>-1.023149403824343</v>
+        <v>-0.0836455322957689</v>
       </c>
       <c r="D48" t="n">
         <v>1.46657845948133</v>
       </c>
       <c r="E48" t="n">
-        <v>0.6794550585852722</v>
+        <v>0.6794550585852724</v>
       </c>
       <c r="F48" t="n">
         <v>1.945287974905225</v>
@@ -2559,7 +2559,7 @@
         <v>-0.6353696406569279</v>
       </c>
       <c r="L48" t="n">
-        <v>1.62918719455355</v>
+        <v>1.594375480852882</v>
       </c>
       <c r="M48" t="n">
         <v>0.7037713167782218</v>
@@ -2570,19 +2570,19 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B49" t="n">
-        <v>1.193050738284573</v>
+        <v>-1.235742764809157</v>
       </c>
       <c r="C49" t="n">
-        <v>-1.023149403824343</v>
+        <v>-0.0836455322957689</v>
       </c>
       <c r="D49" t="n">
         <v>-1.20517484870554</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F49" t="n">
         <v>0.06389317760816279</v>
@@ -2603,7 +2603,7 @@
         <v>-0.5187442006946303</v>
       </c>
       <c r="L49" t="n">
-        <v>0.6422308228494882</v>
+        <v>0.6285067922238505</v>
       </c>
       <c r="M49" t="n">
         <v>-1.406938496100678</v>
@@ -2614,19 +2614,19 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B50" t="n">
-        <v>1.193050738284573</v>
+        <v>-1.235742764809157</v>
       </c>
       <c r="C50" t="n">
-        <v>-1.023149403824343</v>
+        <v>-0.0836455322957689</v>
       </c>
       <c r="D50" t="n">
         <v>1.46657845948133</v>
       </c>
       <c r="E50" t="n">
-        <v>-8.167866258961605e-17</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
         <v>1.723947410517335</v>
@@ -2647,7 +2647,7 @@
         <v>-0.5187442006946303</v>
       </c>
       <c r="L50" t="n">
-        <v>2.616143566257612</v>
+        <v>2.560244169481913</v>
       </c>
       <c r="M50" t="n">
         <v>-1.406938496100678</v>
@@ -2658,19 +2658,19 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>-0.2553446907000148</v>
+        <v>-2.947396846622059e-16</v>
       </c>
       <c r="B51" t="n">
-        <v>1.193050738284573</v>
+        <v>-1.235742764809157</v>
       </c>
       <c r="C51" t="n">
-        <v>-1.023149403824343</v>
+        <v>-0.0836455322957689</v>
       </c>
       <c r="D51" t="n">
         <v>1.46657845948133</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F51" t="n">
         <v>-0.0240896967360233</v>
@@ -2691,7 +2691,7 @@
         <v>1.46388827866443</v>
       </c>
       <c r="L51" t="n">
-        <v>0.2770569653189853</v>
+        <v>0.2711353774311089</v>
       </c>
       <c r="M51" t="n">
         <v>-1.758723464913828</v>
@@ -2702,19 +2702,19 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B52" t="n">
-        <v>1.193050738284573</v>
+        <v>-1.235742764809157</v>
       </c>
       <c r="C52" t="n">
-        <v>-1.023149403824343</v>
+        <v>-0.0836455322957689</v>
       </c>
       <c r="D52" t="n">
         <v>1.46657845948133</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F52" t="n">
         <v>-0.1021122456827544</v>
@@ -2735,7 +2735,7 @@
         <v>-0.4021187607323326</v>
       </c>
       <c r="L52" t="n">
-        <v>1.62918719455355</v>
+        <v>1.594375480852882</v>
       </c>
       <c r="M52" t="n">
         <v>1.055556285591372</v>
@@ -2746,13 +2746,13 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B53" t="n">
-        <v>1.193050738284573</v>
+        <v>-1.235742764809157</v>
       </c>
       <c r="C53" t="n">
-        <v>-1.023149403824343</v>
+        <v>-0.0836455322957689</v>
       </c>
       <c r="D53" t="n">
         <v>1.46657845948133</v>
@@ -2779,7 +2779,7 @@
         <v>-0.6353696406569279</v>
       </c>
       <c r="L53" t="n">
-        <v>1.431795920212737</v>
+        <v>1.401201743127076</v>
       </c>
       <c r="M53" t="n">
         <v>1.055556285591372</v>
@@ -2790,19 +2790,19 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B54" t="n">
-        <v>1.193050738284573</v>
+        <v>-1.235742764809157</v>
       </c>
       <c r="C54" t="n">
-        <v>-1.023149403824343</v>
+        <v>-0.0836455322957689</v>
       </c>
       <c r="D54" t="n">
         <v>1.46657845948133</v>
       </c>
       <c r="E54" t="n">
-        <v>0.3016562502268909</v>
+        <v>0.3016562502268911</v>
       </c>
       <c r="F54" t="n">
         <v>1.336601422838528</v>
@@ -2823,7 +2823,7 @@
         <v>-0.8686205205815232</v>
       </c>
       <c r="L54" t="n">
-        <v>1.826578468894362</v>
+        <v>1.787549218578688</v>
       </c>
       <c r="M54" t="n">
         <v>-0.3515835896612282</v>
@@ -2834,19 +2834,19 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B55" t="n">
-        <v>1.193050738284573</v>
+        <v>-1.235742764809157</v>
       </c>
       <c r="C55" t="n">
-        <v>-1.023149403824343</v>
+        <v>-0.0836455322957689</v>
       </c>
       <c r="D55" t="n">
         <v>1.46657845948133</v>
       </c>
       <c r="E55" t="n">
-        <v>0.3016562502268909</v>
+        <v>0.3016562502268911</v>
       </c>
       <c r="F55" t="n">
         <v>0.4512391652869696</v>
@@ -2867,7 +2867,7 @@
         <v>-0.5187442006946303</v>
       </c>
       <c r="L55" t="n">
-        <v>0.2474482741678634</v>
+        <v>0.242159316772238</v>
       </c>
       <c r="M55" t="n">
         <v>-0.3515835896612282</v>
@@ -2878,13 +2878,13 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B56" t="n">
-        <v>1.193050738284573</v>
+        <v>-1.235742764809157</v>
       </c>
       <c r="C56" t="n">
-        <v>-1.023149403824343</v>
+        <v>-0.0836455322957689</v>
       </c>
       <c r="D56" t="n">
         <v>1.46657845948133</v>
@@ -2911,7 +2911,7 @@
         <v>-0.9852459605438209</v>
       </c>
       <c r="L56" t="n">
-        <v>1.826578468894362</v>
+        <v>1.787549218578688</v>
       </c>
       <c r="M56" t="n">
         <v>0.7037713167782218</v>
@@ -2922,19 +2922,19 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B57" t="n">
-        <v>1.193050738284573</v>
+        <v>-1.235742764809157</v>
       </c>
       <c r="C57" t="n">
-        <v>-1.023149403824343</v>
+        <v>-0.0836455322957689</v>
       </c>
       <c r="D57" t="n">
         <v>-1.20517484870554</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F57" t="n">
         <v>0.5065743063839421</v>
@@ -2955,7 +2955,7 @@
         <v>1.347262838702132</v>
       </c>
       <c r="L57" t="n">
-        <v>-0.9368993718770108</v>
+        <v>-0.9168831095825996</v>
       </c>
       <c r="M57" t="n">
         <v>1.055556285591372</v>
@@ -2966,13 +2966,13 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B58" t="n">
-        <v>1.193050738284573</v>
+        <v>-1.235742764809157</v>
       </c>
       <c r="C58" t="n">
-        <v>-1.023149403824343</v>
+        <v>-0.0836455322957689</v>
       </c>
       <c r="D58" t="n">
         <v>1.46657845948133</v>
@@ -2999,7 +2999,7 @@
         <v>1.580513718626727</v>
       </c>
       <c r="L58" t="n">
-        <v>2.616143566257612</v>
+        <v>2.560244169481913</v>
       </c>
       <c r="M58" t="n">
         <v>-0.3515835896612282</v>
@@ -3010,13 +3010,13 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B59" t="n">
-        <v>1.193050738284573</v>
+        <v>-1.235742764809157</v>
       </c>
       <c r="C59" t="n">
-        <v>-1.023149403824343</v>
+        <v>-0.0836455322957689</v>
       </c>
       <c r="D59" t="n">
         <v>1.46657845948133</v>
@@ -3043,7 +3043,7 @@
         <v>-0.6353696406569279</v>
       </c>
       <c r="L59" t="n">
-        <v>-0.1493081872571694</v>
+        <v>-0.1461198960566325</v>
       </c>
       <c r="M59" t="n">
         <v>0.7037713167782218</v>
@@ -3054,19 +3054,19 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B60" t="n">
-        <v>1.193050738284573</v>
+        <v>-1.235742764809157</v>
       </c>
       <c r="C60" t="n">
-        <v>-1.023149403824343</v>
+        <v>-0.0836455322957689</v>
       </c>
       <c r="D60" t="n">
         <v>1.46657845948133</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F60" t="n">
         <v>0.06389317760816279</v>
@@ -3087,7 +3087,7 @@
         <v>1.46388827866443</v>
       </c>
       <c r="L60" t="n">
-        <v>0.6422308228494882</v>
+        <v>0.6285067922238505</v>
       </c>
       <c r="M60" t="n">
         <v>0.7037713167782218</v>
@@ -3098,13 +3098,13 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B61" t="n">
-        <v>1.193050738284573</v>
+        <v>-1.235742764809157</v>
       </c>
       <c r="C61" t="n">
-        <v>-1.023149403824343</v>
+        <v>-0.0836455322957689</v>
       </c>
       <c r="D61" t="n">
         <v>1.46657845948133</v>
@@ -3131,7 +3131,7 @@
         <v>-0.7519950806192256</v>
       </c>
       <c r="L61" t="n">
-        <v>0.2474482741678634</v>
+        <v>0.242159316772238</v>
       </c>
       <c r="M61" t="n">
         <v>0.7037713167782218</v>
@@ -3142,19 +3142,19 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B62" t="n">
-        <v>1.193050738284573</v>
+        <v>-1.235742764809157</v>
       </c>
       <c r="C62" t="n">
-        <v>-1.023149403824343</v>
+        <v>-0.0836455322957689</v>
       </c>
       <c r="D62" t="n">
         <v>1.46657845948133</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F62" t="n">
         <v>0.06389317760816279</v>
@@ -3175,7 +3175,7 @@
         <v>-0.6353696406569279</v>
       </c>
       <c r="L62" t="n">
-        <v>0.6422308228494882</v>
+        <v>0.6285067922238505</v>
       </c>
       <c r="M62" t="n">
         <v>0.7037713167782218</v>
@@ -3186,19 +3186,19 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B63" t="n">
-        <v>1.193050738284573</v>
+        <v>-1.235742764809157</v>
       </c>
       <c r="C63" t="n">
-        <v>-1.023149403824343</v>
+        <v>-0.0836455322957689</v>
       </c>
       <c r="D63" t="n">
         <v>1.46657845948133</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F63" t="n">
         <v>0.06389317760816279</v>
@@ -3219,7 +3219,7 @@
         <v>-0.8686205205815232</v>
       </c>
       <c r="L63" t="n">
-        <v>-0.542116823195386</v>
+        <v>-0.530535634130987</v>
       </c>
       <c r="M63" t="n">
         <v>-1.406938496100678</v>
@@ -3230,13 +3230,13 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B64" t="n">
-        <v>1.193050738284573</v>
+        <v>-1.235742764809157</v>
       </c>
       <c r="C64" t="n">
-        <v>-1.023149403824343</v>
+        <v>-0.0836455322957689</v>
       </c>
       <c r="D64" t="n">
         <v>1.46657845948133</v>
@@ -3263,7 +3263,7 @@
         <v>-0.6353696406569279</v>
       </c>
       <c r="L64" t="n">
-        <v>1.037013371531113</v>
+        <v>1.014854267675463</v>
       </c>
       <c r="M64" t="n">
         <v>-1.406938496100678</v>
@@ -3274,13 +3274,13 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B65" t="n">
-        <v>1.193050738284573</v>
+        <v>-1.235742764809157</v>
       </c>
       <c r="C65" t="n">
-        <v>-1.023149403824343</v>
+        <v>-0.0836455322957689</v>
       </c>
       <c r="D65" t="n">
         <v>1.46657845948133</v>
@@ -3307,7 +3307,7 @@
         <v>-0.8686205205815232</v>
       </c>
       <c r="L65" t="n">
-        <v>0.6422308228494882</v>
+        <v>0.6285067922238505</v>
       </c>
       <c r="M65" t="n">
         <v>-0.7033685584743783</v>
@@ -3318,13 +3318,13 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B66" t="n">
-        <v>1.193050738284573</v>
+        <v>-1.235742764809157</v>
       </c>
       <c r="C66" t="n">
-        <v>-1.023149403824343</v>
+        <v>-0.0836455322957689</v>
       </c>
       <c r="D66" t="n">
         <v>1.46657845948133</v>
@@ -3351,7 +3351,7 @@
         <v>-0.7519950806192256</v>
       </c>
       <c r="L66" t="n">
-        <v>1.62918719455355</v>
+        <v>1.594375480852882</v>
       </c>
       <c r="M66" t="n">
         <v>-1.406938496100678</v>
@@ -3362,19 +3362,19 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B67" t="n">
-        <v>1.193050738284573</v>
+        <v>-1.235742764809157</v>
       </c>
       <c r="C67" t="n">
-        <v>-1.023149403824343</v>
+        <v>-0.0836455322957689</v>
       </c>
       <c r="D67" t="n">
         <v>1.46657845948133</v>
       </c>
       <c r="E67" t="n">
-        <v>0.3016562502268909</v>
+        <v>0.3016562502268911</v>
       </c>
       <c r="F67" t="n">
         <v>1.225931140644583</v>
@@ -3395,7 +3395,7 @@
         <v>-0.7519950806192256</v>
       </c>
       <c r="L67" t="n">
-        <v>2.616143566257612</v>
+        <v>2.560244169481913</v>
       </c>
       <c r="M67" t="n">
         <v>1.055556285591372</v>
@@ -3406,13 +3406,13 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B68" t="n">
-        <v>1.193050738284573</v>
+        <v>-1.235742764809157</v>
       </c>
       <c r="C68" t="n">
-        <v>-1.023149403824343</v>
+        <v>-0.0836455322957689</v>
       </c>
       <c r="D68" t="n">
         <v>1.46657845948133</v>
@@ -3439,7 +3439,7 @@
         <v>-0.8686205205815232</v>
       </c>
       <c r="L68" t="n">
-        <v>1.431795920212737</v>
+        <v>1.401201743127076</v>
       </c>
       <c r="M68" t="n">
         <v>1.055556285591372</v>
@@ -3450,19 +3450,19 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B69" t="n">
-        <v>1.193050738284573</v>
+        <v>-1.235742764809157</v>
       </c>
       <c r="C69" t="n">
-        <v>-1.023149403824343</v>
+        <v>-0.0836455322957689</v>
       </c>
       <c r="D69" t="n">
         <v>1.46657845948133</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.8317401748482529</v>
+        <v>-0.831740174848253</v>
       </c>
       <c r="F69" t="n">
         <v>-0.4894582333615613</v>
@@ -3483,7 +3483,7 @@
         <v>-0.9852459605438209</v>
       </c>
       <c r="L69" t="n">
-        <v>-0.9368993718770108</v>
+        <v>-0.9168831095825996</v>
       </c>
       <c r="M69" t="n">
         <v>-0.3515835896612282</v>
@@ -3494,19 +3494,19 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B70" t="n">
-        <v>1.193050738284573</v>
+        <v>-1.235742764809157</v>
       </c>
       <c r="C70" t="n">
-        <v>-1.023149403824343</v>
+        <v>-0.0836455322957689</v>
       </c>
       <c r="D70" t="n">
         <v>1.46657845948133</v>
       </c>
       <c r="E70" t="n">
-        <v>-8.167866258961605e-17</v>
+        <v>0</v>
       </c>
       <c r="F70" t="n">
         <v>0.5065743063839421</v>
@@ -3527,7 +3527,7 @@
         <v>1.347262838702132</v>
       </c>
       <c r="L70" t="n">
-        <v>1.431795920212737</v>
+        <v>1.401201743127076</v>
       </c>
       <c r="M70" t="n">
         <v>1.055556285591372</v>
@@ -3538,19 +3538,19 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B71" t="n">
-        <v>1.193050738284573</v>
+        <v>-1.235742764809157</v>
       </c>
       <c r="C71" t="n">
-        <v>-1.023149403824343</v>
+        <v>-0.0836455322957689</v>
       </c>
       <c r="D71" t="n">
         <v>1.46657845948133</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.8317401748482529</v>
+        <v>-0.831740174848253</v>
       </c>
       <c r="F71" t="n">
         <v>-0.4894582333615613</v>
@@ -3571,7 +3571,7 @@
         <v>1.46388827866443</v>
       </c>
       <c r="L71" t="n">
-        <v>-0.9368993718770108</v>
+        <v>-0.9168831095825996</v>
       </c>
       <c r="M71" t="n">
         <v>0.7037713167782218</v>
@@ -3582,19 +3582,19 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B72" t="n">
-        <v>1.193050738284573</v>
+        <v>-1.235742764809157</v>
       </c>
       <c r="C72" t="n">
-        <v>0.3868746382281623</v>
+        <v>0.9565315009078376</v>
       </c>
       <c r="D72" t="n">
         <v>-1.20517484870554</v>
       </c>
       <c r="E72" t="n">
-        <v>0.6794550585852722</v>
+        <v>0.6794550585852724</v>
       </c>
       <c r="F72" t="n">
         <v>1.059925717353666</v>
@@ -3615,7 +3615,7 @@
         <v>-0.8686205205815232</v>
       </c>
       <c r="L72" t="n">
-        <v>0.2474482741678634</v>
+        <v>0.242159316772238</v>
       </c>
       <c r="M72" t="n">
         <v>-0.7033685584743783</v>
@@ -3626,19 +3626,19 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B73" t="n">
-        <v>1.193050738284573</v>
+        <v>-1.235742764809157</v>
       </c>
       <c r="C73" t="n">
-        <v>-1.023149403824343</v>
+        <v>-0.0836455322957689</v>
       </c>
       <c r="D73" t="n">
         <v>-1.20517484870554</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F73" t="n">
         <v>-0.6001285155555062</v>
@@ -3659,7 +3659,7 @@
         <v>-0.4021187607323326</v>
       </c>
       <c r="L73" t="n">
-        <v>-0.1473342745137612</v>
+        <v>-0.1441881586793745</v>
       </c>
       <c r="M73" t="n">
         <v>-1.406938496100678</v>
@@ -3670,19 +3670,19 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B74" t="n">
-        <v>1.193050738284573</v>
+        <v>-1.235742764809157</v>
       </c>
       <c r="C74" t="n">
-        <v>-1.023149403824343</v>
+        <v>-0.0836455322957689</v>
       </c>
       <c r="D74" t="n">
         <v>1.46657845948133</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.8317401748482529</v>
+        <v>-0.831740174848253</v>
       </c>
       <c r="F74" t="n">
         <v>-0.6554636566524785</v>
@@ -3703,7 +3703,7 @@
         <v>1.580513718626727</v>
       </c>
       <c r="L74" t="n">
-        <v>-0.9368993718770108</v>
+        <v>-0.9168831095825996</v>
       </c>
       <c r="M74" t="n">
         <v>1.055556285591372</v>
@@ -3714,19 +3714,19 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B75" t="n">
-        <v>-0.3808881835002534</v>
+        <v>0.7484665367130705</v>
       </c>
       <c r="C75" t="n">
-        <v>-1.023149403824343</v>
+        <v>-0.0836455322957689</v>
       </c>
       <c r="D75" t="n">
         <v>1.46657845948133</v>
       </c>
       <c r="E75" t="n">
-        <v>0.3016562502268909</v>
+        <v>0.3016562502268911</v>
       </c>
       <c r="F75" t="n">
         <v>1.391936563935501</v>
@@ -3747,7 +3747,7 @@
         <v>-0.6353696406569279</v>
       </c>
       <c r="L75" t="n">
-        <v>1.037013371531113</v>
+        <v>1.014854267675463</v>
       </c>
       <c r="M75" t="n">
         <v>0.7037713167782218</v>
@@ -3758,19 +3758,19 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>-0.7681065740310408</v>
+        <v>-0.6520228310981192</v>
       </c>
       <c r="B76" t="n">
-        <v>1.193050738284573</v>
+        <v>-1.235742764809157</v>
       </c>
       <c r="C76" t="n">
-        <v>0.2740727148639619</v>
+        <v>0.8470391816232474</v>
       </c>
       <c r="D76" t="n">
         <v>-0.5372365216588224</v>
       </c>
       <c r="E76" t="n">
-        <v>0.3016562502268909</v>
+        <v>0.3016562502268911</v>
       </c>
       <c r="F76" t="n">
         <v>-0.2127825278766992</v>
@@ -3791,7 +3791,7 @@
         <v>-0.6353696406569279</v>
       </c>
       <c r="L76" t="n">
-        <v>-1.122039488682346e-16</v>
+        <v>-0.5005995180509437</v>
       </c>
       <c r="M76" t="n">
         <v>-1.406938496100678</v>
@@ -3802,19 +3802,19 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B77" t="n">
-        <v>-0.9173490450093564</v>
+        <v>0.3713219366281158</v>
       </c>
       <c r="C77" t="n">
-        <v>0.4432755999102626</v>
+        <v>-1.233314884783966</v>
       </c>
       <c r="D77" t="n">
         <v>0.7986401324346124</v>
       </c>
       <c r="E77" t="n">
-        <v>0.3016562502268909</v>
+        <v>0.3016562502268911</v>
       </c>
       <c r="F77" t="n">
         <v>0.3129013125445386</v>
@@ -3835,7 +3835,7 @@
         <v>-0.7519950806192256</v>
       </c>
       <c r="L77" t="n">
-        <v>-0.5026385683272235</v>
+        <v>-0.4919008865858257</v>
       </c>
       <c r="M77" t="n">
         <v>-1.406938496100678</v>
@@ -3846,19 +3846,19 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B78" t="n">
-        <v>-0.9173490450093564</v>
+        <v>0.3713219366281158</v>
       </c>
       <c r="C78" t="n">
-        <v>0.4432755999102626</v>
+        <v>-1.233314884783966</v>
       </c>
       <c r="D78" t="n">
         <v>-1.20517484870554</v>
       </c>
       <c r="E78" t="n">
-        <v>0.6794550585852722</v>
+        <v>0.6794550585852724</v>
       </c>
       <c r="F78" t="n">
         <v>0.1430224293768333</v>
@@ -3879,7 +3879,7 @@
         <v>-0.7519950806192256</v>
       </c>
       <c r="L78" t="n">
-        <v>0.5356395347054496</v>
+        <v>0.5241929738519151</v>
       </c>
       <c r="M78" t="n">
         <v>0.7037713167782218</v>
@@ -3890,13 +3890,13 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B79" t="n">
-        <v>-0.9173490450093564</v>
+        <v>0.3713219366281158</v>
       </c>
       <c r="C79" t="n">
-        <v>0.4432755999102626</v>
+        <v>-1.233314884783966</v>
       </c>
       <c r="D79" t="n">
         <v>-1.20517484870554</v>
@@ -3923,7 +3923,7 @@
         <v>-0.7519950806192256</v>
       </c>
       <c r="L79" t="n">
-        <v>0.5356395347054496</v>
+        <v>0.5241929738519151</v>
       </c>
       <c r="M79" t="n">
         <v>0.7037713167782218</v>
@@ -3934,19 +3934,19 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B80" t="n">
-        <v>-0.9173490450093564</v>
+        <v>0.3713219366281158</v>
       </c>
       <c r="C80" t="n">
-        <v>0.4432755999102626</v>
+        <v>-1.233314884783966</v>
       </c>
       <c r="D80" t="n">
         <v>-1.20517484870554</v>
       </c>
       <c r="E80" t="n">
-        <v>0.3016562502268909</v>
+        <v>0.3016562502268911</v>
       </c>
       <c r="F80" t="n">
         <v>-0.0495438616406306</v>
@@ -3967,7 +3967,7 @@
         <v>-0.7519950806192256</v>
       </c>
       <c r="L80" t="n">
-        <v>-0.09798645592855811</v>
+        <v>-0.09589472424792291</v>
       </c>
       <c r="M80" t="n">
         <v>0.7037713167782218</v>
@@ -3978,13 +3978,13 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B81" t="n">
-        <v>-0.9173490450093564</v>
+        <v>0.3713219366281158</v>
       </c>
       <c r="C81" t="n">
-        <v>0.4432755999102626</v>
+        <v>-1.233314884783966</v>
       </c>
       <c r="D81" t="n">
         <v>-1.20517484870554</v>
@@ -4011,7 +4011,7 @@
         <v>-0.7519950806192256</v>
       </c>
       <c r="L81" t="n">
-        <v>-0.0288995099092738</v>
+        <v>-0.0282839160438907</v>
       </c>
       <c r="M81" t="n">
         <v>0.7037713167782218</v>
@@ -4022,13 +4022,13 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B82" t="n">
-        <v>-1.307229335176667</v>
+        <v>0.0972982871040242</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.459139787003341</v>
+        <v>0.2995775852002966</v>
       </c>
       <c r="D82" t="n">
         <v>-1.20517484870554</v>
@@ -4055,7 +4055,7 @@
         <v>-0.7519950806192256</v>
       </c>
       <c r="L82" t="n">
-        <v>0.4270743338180027</v>
+        <v>0.4179474181027217</v>
       </c>
       <c r="M82" t="n">
         <v>-1.406938496100678</v>
@@ -4066,13 +4066,13 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B83" t="n">
-        <v>-1.307229335176667</v>
+        <v>0.0972982871040242</v>
       </c>
       <c r="C83" t="n">
-        <v>-0.459139787003341</v>
+        <v>0.2995775852002966</v>
       </c>
       <c r="D83" t="n">
         <v>-1.20517484870554</v>
@@ -4099,7 +4099,7 @@
         <v>-0.7519950806192256</v>
       </c>
       <c r="L83" t="n">
-        <v>0.3066656564701072</v>
+        <v>0.3001114380899798</v>
       </c>
       <c r="M83" t="n">
         <v>-0.3515835896612282</v>
@@ -4110,13 +4110,13 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B84" t="n">
-        <v>-1.307229335176667</v>
+        <v>0.0972982871040242</v>
       </c>
       <c r="C84" t="n">
-        <v>-0.459139787003341</v>
+        <v>0.2995775852002966</v>
       </c>
       <c r="D84" t="n">
         <v>-1.20517484870554</v>
@@ -4143,7 +4143,7 @@
         <v>-0.8686205205815232</v>
       </c>
       <c r="L84" t="n">
-        <v>-0.3447255488545736</v>
+        <v>-0.3373618964051808</v>
       </c>
       <c r="M84" t="n">
         <v>-0.3515835896612282</v>
@@ -4154,13 +4154,13 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B85" t="n">
-        <v>-1.307229335176667</v>
+        <v>0.0972982871040242</v>
       </c>
       <c r="C85" t="n">
-        <v>-0.459139787003341</v>
+        <v>0.2995775852002966</v>
       </c>
       <c r="D85" t="n">
         <v>-1.20517484870554</v>
@@ -4187,7 +4187,7 @@
         <v>-0.9852459605438209</v>
       </c>
       <c r="L85" t="n">
-        <v>-0.048638637343355</v>
+        <v>-0.0476012898164713</v>
       </c>
       <c r="M85" t="n">
         <v>-1.406938496100678</v>
@@ -4198,19 +4198,19 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B86" t="n">
-        <v>-1.307229335176667</v>
+        <v>0.0972982871040242</v>
       </c>
       <c r="C86" t="n">
-        <v>-0.459139787003341</v>
+        <v>0.2995775852002966</v>
       </c>
       <c r="D86" t="n">
         <v>-1.20517484870554</v>
       </c>
       <c r="E86" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F86" t="n">
         <v>-0.8474765962589728</v>
@@ -4231,7 +4231,7 @@
         <v>-0.7519950806192256</v>
       </c>
       <c r="L86" t="n">
-        <v>-0.1552299254873937</v>
+        <v>-0.1519151081884067</v>
       </c>
       <c r="M86" t="n">
         <v>0.7037713167782218</v>
@@ -4242,19 +4242,19 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B87" t="n">
-        <v>-1.307229335176667</v>
+        <v>0.0972982871040242</v>
       </c>
       <c r="C87" t="n">
-        <v>-0.459139787003341</v>
+        <v>0.2995775852002966</v>
       </c>
       <c r="D87" t="n">
         <v>-1.20517484870554</v>
       </c>
       <c r="E87" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F87" t="n">
         <v>-0.5680341337192621</v>
@@ -4275,7 +4275,7 @@
         <v>-0.8686205205815232</v>
       </c>
       <c r="L87" t="n">
-        <v>-0.7395080975361984</v>
+        <v>-0.7237093718567933</v>
       </c>
       <c r="M87" t="n">
         <v>0.7037713167782218</v>
@@ -4286,19 +4286,19 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B88" t="n">
-        <v>-1.307229335176667</v>
+        <v>0.0972982871040242</v>
       </c>
       <c r="C88" t="n">
-        <v>-0.459139787003341</v>
+        <v>0.2995775852002966</v>
       </c>
       <c r="D88" t="n">
         <v>-1.20517484870554</v>
       </c>
       <c r="E88" t="n">
-        <v>0.6794550585852722</v>
+        <v>0.6794550585852724</v>
       </c>
       <c r="F88" t="n">
         <v>0.5110011176716999</v>
@@ -4319,7 +4319,7 @@
         <v>-0.7519950806192256</v>
       </c>
       <c r="L88" t="n">
-        <v>0.050056999827051</v>
+        <v>0.0489855790464317</v>
       </c>
       <c r="M88" t="n">
         <v>1.055556285591372</v>
@@ -4330,19 +4330,19 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B89" t="n">
-        <v>-1.307229335176667</v>
+        <v>0.0972982871040242</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.459139787003341</v>
+        <v>0.2995775852002966</v>
       </c>
       <c r="D89" t="n">
         <v>-1.20517484870554</v>
       </c>
       <c r="E89" t="n">
-        <v>-0.8317401748482529</v>
+        <v>-0.831740174848253</v>
       </c>
       <c r="F89" t="n">
         <v>-0.9443130931786744</v>
@@ -4363,7 +4363,7 @@
         <v>-0.6353696406569279</v>
       </c>
       <c r="L89" t="n">
-        <v>-0.9368993718770108</v>
+        <v>-0.9168831095825996</v>
       </c>
       <c r="M89" t="n">
         <v>-0.7033685584743783</v>
@@ -4374,19 +4374,19 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B90" t="n">
-        <v>-1.307229335176667</v>
+        <v>0.0972982871040242</v>
       </c>
       <c r="C90" t="n">
-        <v>-0.459139787003341</v>
+        <v>0.2995775852002966</v>
       </c>
       <c r="D90" t="n">
         <v>-1.20517484870554</v>
       </c>
       <c r="E90" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F90" t="n">
         <v>-0.5414732659927154</v>
@@ -4398,7 +4398,7 @@
         <v>-0.7015373062563826</v>
       </c>
       <c r="I90" t="n">
-        <v>48.65244259844658</v>
+        <v>48.96916666666667</v>
       </c>
       <c r="J90" t="n">
         <v>-0.10828199451529</v>
@@ -4407,7 +4407,7 @@
         <v>1.347262838702132</v>
       </c>
       <c r="L90" t="n">
-        <v>-0.8579428621406858</v>
+        <v>-0.839613614492277</v>
       </c>
       <c r="M90" t="n">
         <v>1.055556285591372</v>
@@ -4418,19 +4418,19 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B91" t="n">
-        <v>-1.307229335176667</v>
+        <v>0.0972982871040242</v>
       </c>
       <c r="C91" t="n">
-        <v>-0.459139787003341</v>
+        <v>0.2995775852002966</v>
       </c>
       <c r="D91" t="n">
         <v>-1.20517484870554</v>
       </c>
       <c r="E91" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F91" t="n">
         <v>-0.8491366504918819</v>
@@ -4451,7 +4451,7 @@
         <v>1.697139158589025</v>
       </c>
       <c r="L91" t="n">
-        <v>-0.048638637343355</v>
+        <v>-0.0476012898164713</v>
       </c>
       <c r="M91" t="n">
         <v>0.7037713167782218</v>
@@ -4462,19 +4462,19 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B92" t="n">
-        <v>-1.307229335176667</v>
+        <v>0.0972982871040242</v>
       </c>
       <c r="C92" t="n">
-        <v>-0.459139787003341</v>
+        <v>0.2995775852002966</v>
       </c>
       <c r="D92" t="n">
         <v>0.7986401324346124</v>
       </c>
       <c r="E92" t="n">
-        <v>-8.167866258961605e-17</v>
+        <v>0</v>
       </c>
       <c r="F92" t="n">
         <v>-0.046777104585782</v>
@@ -4495,7 +4495,7 @@
         <v>-0.6353696406569279</v>
       </c>
       <c r="L92" t="n">
-        <v>-0.7098994063850765</v>
+        <v>-0.6947333111979224</v>
       </c>
       <c r="M92" t="n">
         <v>-0.7033685584743783</v>
@@ -4506,19 +4506,19 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B93" t="n">
-        <v>-1.307229335176667</v>
+        <v>0.0972982871040242</v>
       </c>
       <c r="C93" t="n">
-        <v>-0.459139787003341</v>
+        <v>0.2995775852002966</v>
       </c>
       <c r="D93" t="n">
         <v>-1.20517484870554</v>
       </c>
       <c r="E93" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F93" t="n">
         <v>-0.9963281258098284</v>
@@ -4539,7 +4539,7 @@
         <v>-0.7519950806192256</v>
       </c>
       <c r="L93" t="n">
-        <v>0.0224222214193373</v>
+        <v>0.0219412557648188</v>
       </c>
       <c r="M93" t="n">
         <v>0.7037713167782218</v>
@@ -4550,19 +4550,19 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B94" t="n">
-        <v>-0.2667475746685293</v>
+        <v>0.8284142399568858</v>
       </c>
       <c r="C94" t="n">
-        <v>0.4996765615923628</v>
+        <v>1.011277660550133</v>
       </c>
       <c r="D94" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E94" t="n">
-        <v>-0.8317401748482529</v>
+        <v>-0.831740174848253</v>
       </c>
       <c r="F94" t="n">
         <v>-0.9459731474115836</v>
@@ -4583,7 +4583,7 @@
         <v>1.114011958777537</v>
       </c>
       <c r="L94" t="n">
-        <v>-0.9368993718770108</v>
+        <v>-0.9168831095825996</v>
       </c>
       <c r="M94" t="n">
         <v>0.7037713167782218</v>
@@ -4594,19 +4594,19 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B95" t="n">
-        <v>-0.2667475746685293</v>
+        <v>0.8284142399568858</v>
       </c>
       <c r="C95" t="n">
-        <v>0.4996765615923628</v>
+        <v>1.011277660550133</v>
       </c>
       <c r="D95" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E95" t="n">
-        <v>-8.167866258961605e-17</v>
+        <v>0</v>
       </c>
       <c r="F95" t="n">
         <v>-0.8629704357661251</v>
@@ -4627,7 +4627,7 @@
         <v>1.580513718626727</v>
       </c>
       <c r="L95" t="n">
-        <v>-0.9368993718770108</v>
+        <v>-0.9168831095825996</v>
       </c>
       <c r="M95" t="n">
         <v>-1.406938496100678</v>
@@ -4638,19 +4638,19 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B96" t="n">
-        <v>-0.2667475746685293</v>
+        <v>0.8284142399568858</v>
       </c>
       <c r="C96" t="n">
-        <v>0.4996765615923628</v>
+        <v>1.011277660550133</v>
       </c>
       <c r="D96" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E96" t="n">
-        <v>0.3016562502268909</v>
+        <v>0.3016562502268911</v>
       </c>
       <c r="F96" t="n">
         <v>-0.046777104585782</v>
@@ -4671,7 +4671,7 @@
         <v>-0.9852459605438209</v>
       </c>
       <c r="L96" t="n">
-        <v>1.382448101627535</v>
+        <v>1.352908308695624</v>
       </c>
       <c r="M96" t="n">
         <v>-1.406938496100678</v>
@@ -4682,19 +4682,19 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B97" t="n">
-        <v>-0.3808881835002534</v>
+        <v>0.7484665367130705</v>
       </c>
       <c r="C97" t="n">
-        <v>0.4996765615923628</v>
+        <v>1.011277660550133</v>
       </c>
       <c r="D97" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E97" t="n">
-        <v>-0.8317401748482529</v>
+        <v>-0.831740174848253</v>
       </c>
       <c r="F97" t="n">
         <v>-0.9459731474115836</v>
@@ -4715,7 +4715,7 @@
         <v>1.114011958777537</v>
       </c>
       <c r="L97" t="n">
-        <v>-0.9368993718770108</v>
+        <v>-0.9168831095825996</v>
       </c>
       <c r="M97" t="n">
         <v>1.055556285591372</v>
@@ -4726,19 +4726,19 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B98" t="n">
-        <v>-0.2667475746685293</v>
+        <v>0.8284142399568858</v>
       </c>
       <c r="C98" t="n">
-        <v>0.4996765615923628</v>
+        <v>1.011277660550133</v>
       </c>
       <c r="D98" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E98" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F98" t="n">
         <v>-0.9487399044664324</v>
@@ -4750,7 +4750,7 @@
         <v>-1.061400257212314</v>
       </c>
       <c r="I98" t="n">
-        <v>51.04595546325565</v>
+        <v>51.06179166666666</v>
       </c>
       <c r="J98" t="n">
         <v>-1.589382247207237</v>
@@ -4759,7 +4759,7 @@
         <v>1.230637398739834</v>
       </c>
       <c r="L98" t="n">
-        <v>0.0105787449588886</v>
+        <v>0.0103508315012704</v>
       </c>
       <c r="M98" t="n">
         <v>-0.3515835896612282</v>
@@ -4770,19 +4770,19 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B99" t="n">
-        <v>-0.2667475746685293</v>
+        <v>0.8284142399568858</v>
       </c>
       <c r="C99" t="n">
-        <v>0.4996765615923628</v>
+        <v>1.011277660550133</v>
       </c>
       <c r="D99" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E99" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F99" t="n">
         <v>-0.9487399044664324</v>
@@ -4803,7 +4803,7 @@
         <v>-0.4021187607323326</v>
       </c>
       <c r="L99" t="n">
-        <v>0.0105787449588886</v>
+        <v>0.0103508315012704</v>
       </c>
       <c r="M99" t="n">
         <v>0.7037713167782218</v>
@@ -4814,19 +4814,19 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B100" t="n">
-        <v>-0.2667475746685293</v>
+        <v>0.8284142399568858</v>
       </c>
       <c r="C100" t="n">
-        <v>0.4996765615923628</v>
+        <v>1.011277660550133</v>
       </c>
       <c r="D100" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E100" t="n">
-        <v>0.6794550585852722</v>
+        <v>0.6794550585852724</v>
       </c>
       <c r="F100" t="n">
         <v>-0.1159460309569975</v>
@@ -4847,7 +4847,7 @@
         <v>-0.7519950806192256</v>
       </c>
       <c r="L100" t="n">
-        <v>0.6915786414346913</v>
+        <v>0.676800226655302</v>
       </c>
       <c r="M100" t="n">
         <v>0.7037713167782218</v>
@@ -4858,19 +4858,19 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>-0.7681065740310408</v>
+        <v>-0.6520228310981192</v>
       </c>
       <c r="B101" t="n">
-        <v>-0.2667475746685293</v>
+        <v>0.8284142399568858</v>
       </c>
       <c r="C101" t="n">
-        <v>-0.459139787003341</v>
+        <v>0.2995775852002966</v>
       </c>
       <c r="D101" t="n">
         <v>0.7986401324346124</v>
       </c>
       <c r="E101" t="n">
-        <v>0.3016562502268909</v>
+        <v>0.3016562502268911</v>
       </c>
       <c r="F101" t="n">
         <v>1.170595999547611</v>
@@ -4891,7 +4891,7 @@
         <v>-0.7519950806192256</v>
       </c>
       <c r="L101" t="n">
-        <v>0.3461439113382696</v>
+        <v>0.3387461856351411</v>
       </c>
       <c r="M101" t="n">
         <v>0.3519863479650718</v>
@@ -4902,13 +4902,13 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B102" t="n">
-        <v>-0.2667475746685293</v>
+        <v>0.8284142399568858</v>
       </c>
       <c r="C102" t="n">
-        <v>0.4996765615923628</v>
+        <v>1.011277660550133</v>
       </c>
       <c r="D102" t="n">
         <v>0.130701805387895</v>
@@ -4935,7 +4935,7 @@
         <v>-0.5187442006946303</v>
       </c>
       <c r="L102" t="n">
-        <v>0.6915786414346913</v>
+        <v>0.676800226655302</v>
       </c>
       <c r="M102" t="n">
         <v>0.7037713167782218</v>
@@ -4946,19 +4946,19 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B103" t="n">
-        <v>-0.2667475746685293</v>
+        <v>0.8284142399568858</v>
       </c>
       <c r="C103" t="n">
-        <v>0.4996765615923628</v>
+        <v>1.011277660550133</v>
       </c>
       <c r="D103" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E103" t="n">
-        <v>0.3016562502268909</v>
+        <v>0.3016562502268911</v>
       </c>
       <c r="F103" t="n">
         <v>-0.5060587756906531</v>
@@ -4979,7 +4979,7 @@
         <v>1.697139158589025</v>
       </c>
       <c r="L103" t="n">
-        <v>0.6915786414346913</v>
+        <v>0.676800226655302</v>
       </c>
       <c r="M103" t="n">
         <v>-1.406938496100678</v>
@@ -4990,13 +4990,13 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B104" t="n">
-        <v>-0.2667475746685293</v>
+        <v>0.8284142399568858</v>
       </c>
       <c r="C104" t="n">
-        <v>0.4996765615923628</v>
+        <v>1.011277660550133</v>
       </c>
       <c r="D104" t="n">
         <v>0.130701805387895</v>
@@ -5023,7 +5023,7 @@
         <v>1.347262838702132</v>
       </c>
       <c r="L104" t="n">
-        <v>0.9837177274590936</v>
+        <v>0.9626973584894952</v>
       </c>
       <c r="M104" t="n">
         <v>0.7037713167782218</v>
@@ -5034,13 +5034,13 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B105" t="n">
-        <v>-0.2667475746685293</v>
+        <v>0.8284142399568858</v>
       </c>
       <c r="C105" t="n">
-        <v>0.4996765615923628</v>
+        <v>1.011277660550133</v>
       </c>
       <c r="D105" t="n">
         <v>0.130701805387895</v>
@@ -5067,7 +5067,7 @@
         <v>1.580513718626727</v>
       </c>
       <c r="L105" t="n">
-        <v>1.382448101627535</v>
+        <v>1.352908308695624</v>
       </c>
       <c r="M105" t="n">
         <v>-1.406938496100678</v>
@@ -5078,19 +5078,19 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B106" t="n">
-        <v>-0.2667475746685293</v>
+        <v>0.8284142399568858</v>
       </c>
       <c r="C106" t="n">
-        <v>0.4996765615923628</v>
+        <v>1.011277660550133</v>
       </c>
       <c r="D106" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E106" t="n">
-        <v>0.3016562502268909</v>
+        <v>0.3016562502268911</v>
       </c>
       <c r="F106" t="n">
         <v>-0.4756244480873182</v>
@@ -5111,7 +5111,7 @@
         <v>1.697139158589025</v>
       </c>
       <c r="L106" t="n">
-        <v>0.0994048184122541</v>
+        <v>0.0972790134778833</v>
       </c>
       <c r="M106" t="n">
         <v>1.055556285591372</v>
@@ -5122,19 +5122,19 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B107" t="n">
-        <v>-0.2667475746685293</v>
+        <v>0.8284142399568858</v>
       </c>
       <c r="C107" t="n">
-        <v>0.4996765615923628</v>
+        <v>1.011277660550133</v>
       </c>
       <c r="D107" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E107" t="n">
-        <v>-0.8317401748482529</v>
+        <v>-0.831740174848253</v>
       </c>
       <c r="F107" t="n">
         <v>-2.516350882477691e-16</v>
@@ -5155,7 +5155,7 @@
         <v>1.580513718626727</v>
       </c>
       <c r="L107" t="n">
-        <v>-0.9368993718770108</v>
+        <v>-0.9168831095825996</v>
       </c>
       <c r="M107" t="n">
         <v>1.055556285591372</v>
@@ -5166,19 +5166,19 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B108" t="n">
-        <v>-0.2667475746685293</v>
+        <v>0.8284142399568858</v>
       </c>
       <c r="C108" t="n">
-        <v>0.4996765615923628</v>
+        <v>1.011277660550133</v>
       </c>
       <c r="D108" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E108" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F108" t="n">
         <v>-0.4064555217161026</v>
@@ -5199,7 +5199,7 @@
         <v>1.580513718626727</v>
       </c>
       <c r="L108" t="n">
-        <v>-0.9368993718770108</v>
+        <v>-0.9168831095825996</v>
       </c>
       <c r="M108" t="n">
         <v>0.7037713167782218</v>
@@ -5210,19 +5210,19 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B109" t="n">
-        <v>-0.2667475746685293</v>
+        <v>0.8284142399568858</v>
       </c>
       <c r="C109" t="n">
-        <v>0.4996765615923628</v>
+        <v>1.011277660550133</v>
       </c>
       <c r="D109" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E109" t="n">
-        <v>-0.8317401748482529</v>
+        <v>-0.831740174848253</v>
       </c>
       <c r="F109" t="n">
         <v>-1.056643429605528</v>
@@ -5243,7 +5243,7 @@
         <v>1.46388827866443</v>
       </c>
       <c r="L109" t="n">
-        <v>-0.9368993718770108</v>
+        <v>-0.9168831095825996</v>
       </c>
       <c r="M109" t="n">
         <v>1.055556285591372</v>
@@ -5254,13 +5254,13 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B110" t="n">
-        <v>-0.2667475746685293</v>
+        <v>0.8284142399568858</v>
       </c>
       <c r="C110" t="n">
-        <v>0.4996765615923628</v>
+        <v>1.011277660550133</v>
       </c>
       <c r="D110" t="n">
         <v>0.130701805387895</v>
@@ -5287,7 +5287,7 @@
         <v>-0.8686205205815232</v>
       </c>
       <c r="L110" t="n">
-        <v>-1.122039488682346e-16</v>
+        <v>0.3203888672837329</v>
       </c>
       <c r="M110" t="n">
         <v>1.055556285591372</v>
@@ -5298,19 +5298,19 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B111" t="n">
-        <v>-0.2667475746685293</v>
+        <v>0.8284142399568858</v>
       </c>
       <c r="C111" t="n">
-        <v>0.4996765615923628</v>
+        <v>1.011277660550133</v>
       </c>
       <c r="D111" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E111" t="n">
-        <v>-0.8317401748482529</v>
+        <v>-0.831740174848253</v>
       </c>
       <c r="F111" t="n">
         <v>-0.8629704357661251</v>
@@ -5331,7 +5331,7 @@
         <v>1.46388827866443</v>
       </c>
       <c r="L111" t="n">
-        <v>-0.9368993718770108</v>
+        <v>-0.9168831095825996</v>
       </c>
       <c r="M111" t="n">
         <v>0.7037713167782218</v>
@@ -5342,19 +5342,19 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>-0.2553446907000148</v>
+        <v>-2.947396846622059e-16</v>
       </c>
       <c r="B112" t="n">
-        <v>-0.2667475746685293</v>
+        <v>0.8284142399568858</v>
       </c>
       <c r="C112" t="n">
-        <v>-1.023149403824343</v>
+        <v>-0.0836455322957689</v>
       </c>
       <c r="D112" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E112" t="n">
-        <v>0.6794550585852722</v>
+        <v>0.6794550585852724</v>
       </c>
       <c r="F112" t="n">
         <v>-0.3234528100706441</v>
@@ -5375,7 +5375,7 @@
         <v>1.580513718626727</v>
       </c>
       <c r="L112" t="n">
-        <v>0.0994048184122541</v>
+        <v>0.0972790134778833</v>
       </c>
       <c r="M112" t="n">
         <v>-1.758723464913828</v>
@@ -5386,19 +5386,19 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B113" t="n">
-        <v>-0.2667475746685293</v>
+        <v>0.8284142399568858</v>
       </c>
       <c r="C113" t="n">
-        <v>0.4996765615923628</v>
+        <v>1.011277660550133</v>
       </c>
       <c r="D113" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E113" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F113" t="n">
         <v>-0.6277960861039923</v>
@@ -5419,7 +5419,7 @@
         <v>-0.6353696406569279</v>
       </c>
       <c r="L113" t="n">
-        <v>-0.9368993718770108</v>
+        <v>-0.9168831095825996</v>
       </c>
       <c r="M113" t="n">
         <v>0.7037713167782218</v>
@@ -5430,19 +5430,19 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B114" t="n">
-        <v>-0.2667475746685293</v>
+        <v>0.8284142399568858</v>
       </c>
       <c r="C114" t="n">
-        <v>0.4996765615923628</v>
+        <v>1.011277660550133</v>
       </c>
       <c r="D114" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E114" t="n">
-        <v>0.3016562502268909</v>
+        <v>0.3016562502268911</v>
       </c>
       <c r="F114" t="n">
         <v>0.2575661714475662</v>
@@ -5463,7 +5463,7 @@
         <v>-0.6353696406569279</v>
       </c>
       <c r="L114" t="n">
-        <v>0.2967960927530665</v>
+        <v>0.2904527512036896</v>
       </c>
       <c r="M114" t="n">
         <v>-1.406938496100678</v>
@@ -5474,19 +5474,19 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B115" t="n">
-        <v>-0.2667475746685293</v>
+        <v>0.8284142399568858</v>
       </c>
       <c r="C115" t="n">
-        <v>0.4996765615923628</v>
+        <v>1.011277660550133</v>
       </c>
       <c r="D115" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E115" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F115" t="n">
         <v>-0.7384663682979371</v>
@@ -5507,7 +5507,7 @@
         <v>1.230637398739834</v>
       </c>
       <c r="L115" t="n">
-        <v>-0.9368993718770108</v>
+        <v>-0.9168831095825996</v>
       </c>
       <c r="M115" t="n">
         <v>-1.406938496100678</v>
@@ -5518,19 +5518,19 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B116" t="n">
-        <v>-0.2667475746685293</v>
+        <v>0.8284142399568858</v>
       </c>
       <c r="C116" t="n">
-        <v>0.4996765615923628</v>
+        <v>1.011277660550133</v>
       </c>
       <c r="D116" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E116" t="n">
-        <v>0.6794550585852722</v>
+        <v>0.6794550585852724</v>
       </c>
       <c r="F116" t="n">
         <v>0.5480756622066714</v>
@@ -5551,7 +5551,7 @@
         <v>1.580513718626727</v>
       </c>
       <c r="L116" t="n">
-        <v>1.333100283042332</v>
+        <v>1.304614874264172</v>
       </c>
       <c r="M116" t="n">
         <v>1.055556285591372</v>
@@ -5562,19 +5562,19 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B117" t="n">
-        <v>-0.2667475746685293</v>
+        <v>0.8284142399568858</v>
       </c>
       <c r="C117" t="n">
-        <v>0.4996765615923628</v>
+        <v>1.011277660550133</v>
       </c>
       <c r="D117" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E117" t="n">
-        <v>-0.8317401748482529</v>
+        <v>-0.831740174848253</v>
       </c>
       <c r="F117" t="n">
         <v>-1.056643429605528</v>
@@ -5595,7 +5595,7 @@
         <v>1.46388827866443</v>
       </c>
       <c r="L117" t="n">
-        <v>-0.9368993718770108</v>
+        <v>-0.9168831095825996</v>
       </c>
       <c r="M117" t="n">
         <v>-0.7033685584743783</v>
@@ -5606,13 +5606,13 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B118" t="n">
-        <v>-0.2667475746685293</v>
+        <v>0.8284142399568858</v>
       </c>
       <c r="C118" t="n">
-        <v>-1.023149403824343</v>
+        <v>-0.0836455322957689</v>
       </c>
       <c r="D118" t="n">
         <v>0.130701805387895</v>
@@ -5639,7 +5639,7 @@
         <v>1.347262838702132</v>
       </c>
       <c r="L118" t="n">
-        <v>0.2967960927530665</v>
+        <v>0.2904527512036896</v>
       </c>
       <c r="M118" t="n">
         <v>-1.406938496100678</v>
@@ -5650,13 +5650,13 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B119" t="n">
-        <v>-0.2667475746685293</v>
+        <v>0.8284142399568858</v>
       </c>
       <c r="C119" t="n">
-        <v>0.4996765615923628</v>
+        <v>1.011277660550133</v>
       </c>
       <c r="D119" t="n">
         <v>0.130701805387895</v>
@@ -5674,7 +5674,7 @@
         <v>-1.041407871048096</v>
       </c>
       <c r="I119" t="n">
-        <v>48.65216785446561</v>
+        <v>50.88518670550848</v>
       </c>
       <c r="J119" t="n">
         <v>-1.589382247207237</v>
@@ -5683,7 +5683,7 @@
         <v>1.347262838702132</v>
       </c>
       <c r="L119" t="n">
-        <v>-0.048638637343355</v>
+        <v>-0.0476012898164713</v>
       </c>
       <c r="M119" t="n">
         <v>-0.3515835896612282</v>
@@ -5694,19 +5694,19 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B120" t="n">
-        <v>-0.2667475746685293</v>
+        <v>0.8284142399568858</v>
       </c>
       <c r="C120" t="n">
-        <v>0.4996765615923628</v>
+        <v>1.011277660550133</v>
       </c>
       <c r="D120" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E120" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F120" t="n">
         <v>-0.6969650124752078</v>
@@ -5727,7 +5727,7 @@
         <v>1.230637398739834</v>
       </c>
       <c r="L120" t="n">
-        <v>0.2967960927530665</v>
+        <v>0.2904527512036896</v>
       </c>
       <c r="M120" t="n">
         <v>-0.3515835896612282</v>
@@ -5738,13 +5738,13 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B121" t="n">
-        <v>-0.2667475746685293</v>
+        <v>0.8284142399568858</v>
       </c>
       <c r="C121" t="n">
-        <v>0.4996765615923628</v>
+        <v>1.011277660550133</v>
       </c>
       <c r="D121" t="n">
         <v>0.130701805387895</v>
@@ -5771,7 +5771,7 @@
         <v>1.114011958777537</v>
       </c>
       <c r="L121" t="n">
-        <v>0.6915786414346913</v>
+        <v>0.676800226655302</v>
       </c>
       <c r="M121" t="n">
         <v>0.7037713167782218</v>
@@ -5782,19 +5782,19 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B122" t="n">
-        <v>-0.2667475746685293</v>
+        <v>0.8284142399568858</v>
       </c>
       <c r="C122" t="n">
-        <v>0.4996765615923628</v>
+        <v>1.011277660550133</v>
       </c>
       <c r="D122" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E122" t="n">
-        <v>0.6794550585852722</v>
+        <v>0.6794550585852724</v>
       </c>
       <c r="F122" t="n">
         <v>1.79311633688855</v>
@@ -5815,7 +5815,7 @@
         <v>-0.6353696406569279</v>
       </c>
       <c r="L122" t="n">
-        <v>0.3461439113382696</v>
+        <v>0.3387461856351411</v>
       </c>
       <c r="M122" t="n">
         <v>1.055556285591372</v>
@@ -5826,19 +5826,19 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B123" t="n">
-        <v>-0.2667475746685293</v>
+        <v>0.8284142399568858</v>
       </c>
       <c r="C123" t="n">
-        <v>0.4996765615923628</v>
+        <v>1.011277660550133</v>
       </c>
       <c r="D123" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E123" t="n">
-        <v>-0.8317401748482529</v>
+        <v>-0.831740174848253</v>
       </c>
       <c r="F123" t="n">
         <v>-1.001308288508556</v>
@@ -5859,7 +5859,7 @@
         <v>-0.5187442006946303</v>
       </c>
       <c r="L123" t="n">
-        <v>-1.122039488682346e-16</v>
+        <v>-0.9352404279340076</v>
       </c>
       <c r="M123" t="n">
         <v>1.055556285591372</v>
@@ -5870,19 +5870,19 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>0.257417192631011</v>
+        <v>0.0116719359098847</v>
       </c>
       <c r="B124" t="n">
-        <v>-0.2667475746685293</v>
+        <v>0.8284142399568858</v>
       </c>
       <c r="C124" t="n">
-        <v>0.4996765615923628</v>
+        <v>1.011277660550133</v>
       </c>
       <c r="D124" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E124" t="n">
-        <v>2.190650292018797</v>
+        <v>2.190650292018798</v>
       </c>
       <c r="F124" t="n">
         <v>0.6449121591263731</v>
@@ -5903,7 +5903,7 @@
         <v>1.230637398739834</v>
       </c>
       <c r="L124" t="n">
-        <v>0.0994048184122541</v>
+        <v>0.0972790134778833</v>
       </c>
       <c r="M124" t="n">
         <v>1.055556285591372</v>
@@ -5914,13 +5914,13 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B125" t="n">
-        <v>1.281359525117539</v>
+        <v>-0.8649708077363902</v>
       </c>
       <c r="C125" t="n">
-        <v>0.6688794466386635</v>
+        <v>1.175516139477018</v>
       </c>
       <c r="D125" t="n">
         <v>0.130701805387895</v>
@@ -5947,7 +5947,7 @@
         <v>-0.7519950806192256</v>
       </c>
       <c r="L125" t="n">
-        <v>2.714839203428018</v>
+        <v>2.656831038344816</v>
       </c>
       <c r="M125" t="n">
         <v>0.7037713167782218</v>
@@ -5958,19 +5958,19 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B126" t="n">
-        <v>1.281359525117539</v>
+        <v>-0.8649708077363902</v>
       </c>
       <c r="C126" t="n">
-        <v>0.6688794466386635</v>
+        <v>1.175516139477018</v>
       </c>
       <c r="D126" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E126" t="n">
-        <v>-0.8317401748482529</v>
+        <v>-0.831740174848253</v>
       </c>
       <c r="F126" t="n">
         <v>-0.710798797749451</v>
@@ -5982,7 +5982,7 @@
         <v>1.717541419614047</v>
       </c>
       <c r="I126" t="n">
-        <v>48.90177505938995</v>
+        <v>49.01342600194209</v>
       </c>
       <c r="J126" t="n">
         <v>-1.095682162976588</v>
@@ -5991,7 +5991,7 @@
         <v>-0.7519950806192256</v>
       </c>
       <c r="L126" t="n">
-        <v>-0.9368993718770108</v>
+        <v>-0.9168831095825996</v>
       </c>
       <c r="M126" t="n">
         <v>0.7037713167782218</v>
@@ -6002,19 +6002,19 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B127" t="n">
-        <v>1.281359525117539</v>
+        <v>-0.8649708077363902</v>
       </c>
       <c r="C127" t="n">
-        <v>0.6688794466386635</v>
+        <v>1.175516139477018</v>
       </c>
       <c r="D127" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E127" t="n">
-        <v>-0.8317401748482529</v>
+        <v>-0.831740174848253</v>
       </c>
       <c r="F127" t="n">
         <v>-0.710798797749451</v>
@@ -6035,7 +6035,7 @@
         <v>-0.5187442006946303</v>
       </c>
       <c r="L127" t="n">
-        <v>-0.9368993718770108</v>
+        <v>-0.9168831095825996</v>
       </c>
       <c r="M127" t="n">
         <v>-0.7033685584743783</v>
@@ -6046,19 +6046,19 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B128" t="n">
-        <v>1.281359525117539</v>
+        <v>-0.8649708077363902</v>
       </c>
       <c r="C128" t="n">
-        <v>0.6688794466386635</v>
+        <v>1.175516139477018</v>
       </c>
       <c r="D128" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E128" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F128" t="n">
         <v>0.22989860089908</v>
@@ -6079,7 +6079,7 @@
         <v>-0.5187442006946303</v>
       </c>
       <c r="L128" t="n">
-        <v>3.997882486643298</v>
+        <v>3.912460333562557</v>
       </c>
       <c r="M128" t="n">
         <v>0.7037713167782218</v>
@@ -6090,13 +6090,13 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B129" t="n">
-        <v>1.281359525117539</v>
+        <v>-0.8649708077363902</v>
       </c>
       <c r="C129" t="n">
-        <v>0.6688794466386635</v>
+        <v>1.175516139477018</v>
       </c>
       <c r="D129" t="n">
         <v>0.130701805387895</v>
@@ -6123,7 +6123,7 @@
         <v>-0.8686205205815232</v>
       </c>
       <c r="L129" t="n">
-        <v>1.95488279721589</v>
+        <v>1.913112148100462</v>
       </c>
       <c r="M129" t="n">
         <v>-0.7033685584743783</v>
@@ -6134,19 +6134,19 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B130" t="n">
-        <v>1.281359525117539</v>
+        <v>-0.8649708077363902</v>
       </c>
       <c r="C130" t="n">
-        <v>0.6688794466386635</v>
+        <v>1.175516139477018</v>
       </c>
       <c r="D130" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E130" t="n">
-        <v>-0.8317401748482529</v>
+        <v>-0.831740174848253</v>
       </c>
       <c r="F130" t="n">
         <v>-0.9321393621373406</v>
@@ -6167,7 +6167,7 @@
         <v>1.347262838702132</v>
       </c>
       <c r="L130" t="n">
-        <v>-0.9368993718770108</v>
+        <v>-0.9168831095825996</v>
       </c>
       <c r="M130" t="n">
         <v>0.7037713167782218</v>
@@ -6178,19 +6178,19 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B131" t="n">
-        <v>1.281359525117539</v>
+        <v>-0.8649708077363902</v>
       </c>
       <c r="C131" t="n">
-        <v>0.6688794466386635</v>
+        <v>1.175516139477018</v>
       </c>
       <c r="D131" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E131" t="n">
-        <v>0.3016562502268909</v>
+        <v>0.3016562502268911</v>
       </c>
       <c r="F131" t="n">
         <v>0.8109175824172903</v>
@@ -6211,7 +6211,7 @@
         <v>-0.6353696406569279</v>
       </c>
       <c r="L131" t="n">
-        <v>1.826578468894362</v>
+        <v>1.787549218578688</v>
       </c>
       <c r="M131" t="n">
         <v>1.055556285591372</v>
@@ -6222,19 +6222,19 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B132" t="n">
-        <v>1.281359525117539</v>
+        <v>-0.8649708077363902</v>
       </c>
       <c r="C132" t="n">
-        <v>0.6688794466386635</v>
+        <v>1.175516139477018</v>
       </c>
       <c r="D132" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E132" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F132" t="n">
         <v>0.6172445885778869</v>
@@ -6255,7 +6255,7 @@
         <v>-0.8686205205815232</v>
       </c>
       <c r="L132" t="n">
-        <v>-0.9368993718770108</v>
+        <v>-0.9168831095825996</v>
       </c>
       <c r="M132" t="n">
         <v>0.7037713167782218</v>
@@ -6266,19 +6266,19 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B133" t="n">
-        <v>1.281359525117539</v>
+        <v>-0.8649708077363902</v>
       </c>
       <c r="C133" t="n">
-        <v>0.6688794466386635</v>
+        <v>1.175516139477018</v>
       </c>
       <c r="D133" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E133" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F133" t="n">
         <v>-0.2681176689736717</v>
@@ -6299,7 +6299,7 @@
         <v>-0.5187442006946303</v>
       </c>
       <c r="L133" t="n">
-        <v>2.221361017575988</v>
+        <v>2.1738966940303</v>
       </c>
       <c r="M133" t="n">
         <v>-0.7033685584743783</v>
@@ -6310,19 +6310,19 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B134" t="n">
-        <v>1.281359525117539</v>
+        <v>-0.8649708077363902</v>
       </c>
       <c r="C134" t="n">
-        <v>0.6688794466386635</v>
+        <v>1.175516139477018</v>
       </c>
       <c r="D134" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E134" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F134" t="n">
         <v>-0.2127825278766992</v>
@@ -6343,7 +6343,7 @@
         <v>-0.6353696406569279</v>
       </c>
       <c r="L134" t="n">
-        <v>2.813534840598424</v>
+        <v>2.753417907207719</v>
       </c>
       <c r="M134" t="n">
         <v>0.7037713167782218</v>
@@ -6354,19 +6354,19 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B135" t="n">
-        <v>1.281359525117539</v>
+        <v>-0.8649708077363902</v>
       </c>
       <c r="C135" t="n">
-        <v>0.6688794466386635</v>
+        <v>1.175516139477018</v>
       </c>
       <c r="D135" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E135" t="n">
-        <v>0.3016562502268909</v>
+        <v>0.3016562502268911</v>
       </c>
       <c r="F135" t="n">
         <v>0.8662527235142627</v>
@@ -6387,7 +6387,7 @@
         <v>-0.7519950806192256</v>
       </c>
       <c r="L135" t="n">
-        <v>1.62918719455355</v>
+        <v>1.594375480852882</v>
       </c>
       <c r="M135" t="n">
         <v>0.7037713167782218</v>
@@ -6398,13 +6398,13 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B136" t="n">
-        <v>1.281359525117539</v>
+        <v>-0.8649708077363902</v>
       </c>
       <c r="C136" t="n">
-        <v>0.6688794466386635</v>
+        <v>1.175516139477018</v>
       </c>
       <c r="D136" t="n">
         <v>0.130701805387895</v>
@@ -6431,7 +6431,7 @@
         <v>-0.7519950806192256</v>
       </c>
       <c r="L136" t="n">
-        <v>3.997882486643298</v>
+        <v>3.912460333562557</v>
       </c>
       <c r="M136" t="n">
         <v>1.055556285591372</v>
@@ -6442,19 +6442,19 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>-0.2553446907000148</v>
+        <v>-2.947396846622059e-16</v>
       </c>
       <c r="B137" t="n">
-        <v>1.281359525117539</v>
+        <v>-0.8649708077363902</v>
       </c>
       <c r="C137" t="n">
-        <v>0.6688794466386635</v>
+        <v>1.175516139477018</v>
       </c>
       <c r="D137" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E137" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F137" t="n">
         <v>-0.185114957328213</v>
@@ -6475,7 +6475,7 @@
         <v>-0.6353696406569279</v>
       </c>
       <c r="L137" t="n">
-        <v>-0.048638637343355</v>
+        <v>-0.0476012898164713</v>
       </c>
       <c r="M137" t="n">
         <v>-1.758723464913828</v>
@@ -6486,19 +6486,19 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B138" t="n">
-        <v>1.281359525117539</v>
+        <v>-0.8649708077363902</v>
       </c>
       <c r="C138" t="n">
-        <v>0.6688794466386635</v>
+        <v>1.175516139477018</v>
       </c>
       <c r="D138" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E138" t="n">
-        <v>1.812851483660416</v>
+        <v>1.812851483660417</v>
       </c>
       <c r="F138" t="n">
         <v>4.712045029753845</v>
@@ -6519,7 +6519,7 @@
         <v>-0.8686205205815232</v>
       </c>
       <c r="L138" t="n">
-        <v>1.333100283042332</v>
+        <v>1.304614874264172</v>
       </c>
       <c r="M138" t="n">
         <v>-0.3515835896612282</v>
@@ -6530,19 +6530,19 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>-0.2553446907000148</v>
+        <v>-2.947396846622059e-16</v>
       </c>
       <c r="B139" t="n">
-        <v>1.281359525117539</v>
+        <v>-0.8649708077363902</v>
       </c>
       <c r="C139" t="n">
-        <v>0.6688794466386635</v>
+        <v>1.175516139477018</v>
       </c>
       <c r="D139" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E139" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F139" t="n">
         <v>-0.185114957328213</v>
@@ -6563,7 +6563,7 @@
         <v>-0.7519950806192256</v>
       </c>
       <c r="L139" t="n">
-        <v>-0.048638637343355</v>
+        <v>-0.0476012898164713</v>
       </c>
       <c r="M139" t="n">
         <v>-1.758723464913828</v>
@@ -6574,19 +6574,19 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B140" t="n">
-        <v>1.281359525117539</v>
+        <v>-0.8649708077363902</v>
       </c>
       <c r="C140" t="n">
-        <v>0.6688794466386635</v>
+        <v>1.175516139477018</v>
       </c>
       <c r="D140" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E140" t="n">
-        <v>0.6794550585852722</v>
+        <v>0.6794550585852724</v>
       </c>
       <c r="F140" t="n">
         <v>1.308933852290042</v>
@@ -6607,7 +6607,7 @@
         <v>-0.7519950806192256</v>
       </c>
       <c r="L140" t="n">
-        <v>-1.122039488682346e-16</v>
+        <v>0.4652691705780876</v>
       </c>
       <c r="M140" t="n">
         <v>1.055556285591372</v>
@@ -6618,19 +6618,19 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B141" t="n">
-        <v>1.281359525117539</v>
+        <v>-0.8649708077363902</v>
       </c>
       <c r="C141" t="n">
-        <v>0.6688794466386635</v>
+        <v>1.175516139477018</v>
       </c>
       <c r="D141" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E141" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F141" t="n">
         <v>0.3405688830930248</v>
@@ -6651,7 +6651,7 @@
         <v>-0.6353696406569279</v>
       </c>
       <c r="L141" t="n">
-        <v>-0.3447255488545736</v>
+        <v>-0.3373618964051808</v>
       </c>
       <c r="M141" t="n">
         <v>0.7037713167782218</v>
@@ -6662,19 +6662,19 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B142" t="n">
-        <v>1.281359525117539</v>
+        <v>-0.8649708077363902</v>
       </c>
       <c r="C142" t="n">
-        <v>0.6688794466386635</v>
+        <v>1.175516139477018</v>
       </c>
       <c r="D142" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E142" t="n">
-        <v>0.6794550585852722</v>
+        <v>0.6794550585852724</v>
       </c>
       <c r="F142" t="n">
         <v>3.051990796844673</v>
@@ -6695,7 +6695,7 @@
         <v>-0.5187442006946303</v>
       </c>
       <c r="L142" t="n">
-        <v>2.616143566257612</v>
+        <v>2.560244169481913</v>
       </c>
       <c r="M142" t="n">
         <v>1.055556285591372</v>
@@ -6706,13 +6706,13 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B143" t="n">
-        <v>1.281359525117539</v>
+        <v>-0.8649708077363902</v>
       </c>
       <c r="C143" t="n">
-        <v>0.6688794466386635</v>
+        <v>1.175516139477018</v>
       </c>
       <c r="D143" t="n">
         <v>0.130701805387895</v>
@@ -6739,7 +6739,7 @@
         <v>-0.5187442006946303</v>
       </c>
       <c r="L143" t="n">
-        <v>1.431795920212737</v>
+        <v>1.401201743127076</v>
       </c>
       <c r="M143" t="n">
         <v>0.7037713167782218</v>
@@ -6750,19 +6750,19 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B144" t="n">
-        <v>1.281359525117539</v>
+        <v>-0.8649708077363902</v>
       </c>
       <c r="C144" t="n">
-        <v>0.6688794466386635</v>
+        <v>1.175516139477018</v>
       </c>
       <c r="D144" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E144" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F144" t="n">
         <v>-0.3051922135086432</v>
@@ -6783,7 +6783,7 @@
         <v>1.347262838702132</v>
       </c>
       <c r="L144" t="n">
-        <v>1.526543731896328</v>
+        <v>1.493925137235462</v>
       </c>
       <c r="M144" t="n">
         <v>-0.7033685584743783</v>
@@ -6794,13 +6794,13 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B145" t="n">
-        <v>1.281359525117539</v>
+        <v>-0.8649708077363902</v>
       </c>
       <c r="C145" t="n">
-        <v>0.6688794466386635</v>
+        <v>1.175516139477018</v>
       </c>
       <c r="D145" t="n">
         <v>0.130701805387895</v>
@@ -6827,7 +6827,7 @@
         <v>-0.7519950806192256</v>
       </c>
       <c r="L145" t="n">
-        <v>1.431795920212737</v>
+        <v>1.401201743127076</v>
       </c>
       <c r="M145" t="n">
         <v>-0.3515835896612282</v>
@@ -6838,19 +6838,19 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B146" t="n">
-        <v>1.281359525117539</v>
+        <v>-0.8649708077363902</v>
       </c>
       <c r="C146" t="n">
-        <v>0.6688794466386635</v>
+        <v>1.175516139477018</v>
       </c>
       <c r="D146" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E146" t="n">
-        <v>-0.8317401748482529</v>
+        <v>-0.831740174848253</v>
       </c>
       <c r="F146" t="n">
         <v>-0.9321393621373406</v>
@@ -6871,7 +6871,7 @@
         <v>1.46388827866443</v>
       </c>
       <c r="L146" t="n">
-        <v>-0.9368993718770108</v>
+        <v>-0.9168831095825996</v>
       </c>
       <c r="M146" t="n">
         <v>0.7037713167782218</v>
@@ -6882,19 +6882,19 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B147" t="n">
-        <v>1.281359525117539</v>
+        <v>-0.8649708077363902</v>
       </c>
       <c r="C147" t="n">
-        <v>0.6688794466386635</v>
+        <v>1.175516139477018</v>
       </c>
       <c r="D147" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E147" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F147" t="n">
         <v>-0.3787879511676165</v>
@@ -6915,7 +6915,7 @@
         <v>1.46388827866443</v>
       </c>
       <c r="L147" t="n">
-        <v>-0.9368993718770108</v>
+        <v>-0.9168831095825996</v>
       </c>
       <c r="M147" t="n">
         <v>0.7037713167782218</v>
@@ -6926,13 +6926,13 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B148" t="n">
-        <v>1.281359525117539</v>
+        <v>-0.8649708077363902</v>
       </c>
       <c r="C148" t="n">
-        <v>0.6688794466386635</v>
+        <v>1.175516139477018</v>
       </c>
       <c r="D148" t="n">
         <v>0.130701805387895</v>
@@ -6959,7 +6959,7 @@
         <v>-0.7519950806192256</v>
       </c>
       <c r="L148" t="n">
-        <v>0.1487526369974572</v>
+        <v>0.1455724479093348</v>
       </c>
       <c r="M148" t="n">
         <v>0.7037713167782218</v>
@@ -6970,19 +6970,19 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B149" t="n">
-        <v>1.281359525117539</v>
+        <v>-0.8649708077363902</v>
       </c>
       <c r="C149" t="n">
-        <v>0.6688794466386635</v>
+        <v>1.175516139477018</v>
       </c>
       <c r="D149" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E149" t="n">
-        <v>0.6794550585852722</v>
+        <v>0.6794550585852724</v>
       </c>
       <c r="F149" t="n">
         <v>1.474939275580959</v>
@@ -7003,7 +7003,7 @@
         <v>1.230637398739834</v>
       </c>
       <c r="L149" t="n">
-        <v>1.234404645871925</v>
+        <v>1.208028005401269</v>
       </c>
       <c r="M149" t="n">
         <v>0.7037713167782218</v>
@@ -7014,19 +7014,19 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B150" t="n">
-        <v>1.281359525117539</v>
+        <v>-0.8649708077363902</v>
       </c>
       <c r="C150" t="n">
-        <v>0.6688794466386635</v>
+        <v>1.175516139477018</v>
       </c>
       <c r="D150" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E150" t="n">
-        <v>0.6794550585852722</v>
+        <v>0.6794550585852724</v>
       </c>
       <c r="F150" t="n">
         <v>3.190328649587104</v>
@@ -7047,7 +7047,7 @@
         <v>-0.7519950806192256</v>
       </c>
       <c r="L150" t="n">
-        <v>2.714839203428018</v>
+        <v>2.656831038344816</v>
       </c>
       <c r="M150" t="n">
         <v>-0.7033685584743783</v>
@@ -7058,13 +7058,13 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B151" t="n">
-        <v>1.281359525117539</v>
+        <v>-0.8649708077363902</v>
       </c>
       <c r="C151" t="n">
-        <v>0.6688794466386635</v>
+        <v>1.175516139477018</v>
       </c>
       <c r="D151" t="n">
         <v>0.130701805387895</v>
@@ -7091,7 +7091,7 @@
         <v>-0.6353696406569279</v>
       </c>
       <c r="L151" t="n">
-        <v>1.333100283042332</v>
+        <v>1.304614874264172</v>
       </c>
       <c r="M151" t="n">
         <v>1.055556285591372</v>
@@ -7102,19 +7102,19 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B152" t="n">
-        <v>1.281359525117539</v>
+        <v>-0.8649708077363902</v>
       </c>
       <c r="C152" t="n">
-        <v>0.6688794466386635</v>
+        <v>1.175516139477018</v>
       </c>
       <c r="D152" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E152" t="n">
-        <v>0.3016562502268909</v>
+        <v>0.3016562502268911</v>
       </c>
       <c r="F152" t="n">
         <v>0.9215878646112352</v>
@@ -7135,7 +7135,7 @@
         <v>-0.6353696406569279</v>
       </c>
       <c r="L152" t="n">
-        <v>2.221361017575988</v>
+        <v>2.1738966940303</v>
       </c>
       <c r="M152" t="n">
         <v>1.055556285591372</v>
@@ -7146,19 +7146,19 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>1.282940959293063</v>
+        <v>1.339061469925893</v>
       </c>
       <c r="B153" t="n">
-        <v>0.8067748883961599</v>
+        <v>1.583862102492648</v>
       </c>
       <c r="C153" t="n">
-        <v>0.1612707914997614</v>
+        <v>-1.671284161922326</v>
       </c>
       <c r="D153" t="n">
         <v>0.7986401324346124</v>
       </c>
       <c r="E153" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F153" t="n">
         <v>-0.9459731474115836</v>
@@ -7179,7 +7179,7 @@
         <v>1.46388827866443</v>
       </c>
       <c r="L153" t="n">
-        <v>-0.1177255833626394</v>
+        <v>-0.1152120980205035</v>
       </c>
       <c r="M153" t="n">
         <v>0.7037713167782218</v>
@@ -7190,13 +7190,13 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>1.282940959293063</v>
+        <v>1.339061469925893</v>
       </c>
       <c r="B154" t="n">
-        <v>0.8067748883961599</v>
+        <v>1.583862102492648</v>
       </c>
       <c r="C154" t="n">
-        <v>0.1612707914997614</v>
+        <v>-1.671284161922326</v>
       </c>
       <c r="D154" t="n">
         <v>0.7986401324346124</v>
@@ -7223,7 +7223,7 @@
         <v>-0.9852459605438209</v>
       </c>
       <c r="L154" t="n">
-        <v>-0.463160313459061</v>
+        <v>-0.4532661390406645</v>
       </c>
       <c r="M154" t="n">
         <v>1.055556285591372</v>
@@ -7234,19 +7234,19 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>1.282940959293063</v>
+        <v>1.339061469925893</v>
       </c>
       <c r="B155" t="n">
-        <v>0.8067748883961599</v>
+        <v>1.583862102492648</v>
       </c>
       <c r="C155" t="n">
-        <v>0.1612707914997614</v>
+        <v>-1.671284161922326</v>
       </c>
       <c r="D155" t="n">
         <v>0.7986401324346124</v>
       </c>
       <c r="E155" t="n">
-        <v>0.6794550585852722</v>
+        <v>0.6794550585852724</v>
       </c>
       <c r="F155" t="n">
         <v>-0.6056620296652033</v>
@@ -7267,7 +7267,7 @@
         <v>1.580513718626727</v>
       </c>
       <c r="L155" t="n">
-        <v>-0.463160313459061</v>
+        <v>-0.4532661390406645</v>
       </c>
       <c r="M155" t="n">
         <v>1.055556285591372</v>
@@ -7278,19 +7278,19 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>1.282940959293063</v>
+        <v>1.339061469925893</v>
       </c>
       <c r="B156" t="n">
-        <v>0.8067748883961599</v>
+        <v>1.583862102492648</v>
       </c>
       <c r="C156" t="n">
-        <v>0.1612707914997614</v>
+        <v>-1.671284161922326</v>
       </c>
       <c r="D156" t="n">
         <v>0.7986401324346124</v>
       </c>
       <c r="E156" t="n">
-        <v>-0.8317401748482529</v>
+        <v>-0.831740174848253</v>
       </c>
       <c r="F156" t="n">
         <v>-0.937672876247038</v>
@@ -7311,7 +7311,7 @@
         <v>1.697139158589025</v>
       </c>
       <c r="L156" t="n">
-        <v>-0.9368993718770108</v>
+        <v>-0.9168831095825996</v>
       </c>
       <c r="M156" t="n">
         <v>0.7037713167782218</v>
@@ -7322,19 +7322,19 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>1.282940959293063</v>
+        <v>1.339061469925893</v>
       </c>
       <c r="B157" t="n">
-        <v>0.8067748883961599</v>
+        <v>1.583862102492648</v>
       </c>
       <c r="C157" t="n">
-        <v>0.1612707914997614</v>
+        <v>-1.671284161922326</v>
       </c>
       <c r="D157" t="n">
         <v>0.7986401324346124</v>
       </c>
       <c r="E157" t="n">
-        <v>0.3016562502268909</v>
+        <v>0.3016562502268911</v>
       </c>
       <c r="F157" t="n">
         <v>-0.7611537761476959</v>
@@ -7355,7 +7355,7 @@
         <v>-0.285493320770035</v>
       </c>
       <c r="L157" t="n">
-        <v>-0.0111342952186007</v>
+        <v>-0.0108982796485681</v>
       </c>
       <c r="M157" t="n">
         <v>-1.406938496100678</v>
@@ -7366,19 +7366,19 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>1.282940959293063</v>
+        <v>1.339061469925893</v>
       </c>
       <c r="B158" t="n">
-        <v>0.8067748883961599</v>
+        <v>1.583862102492648</v>
       </c>
       <c r="C158" t="n">
-        <v>0.1612707914997614</v>
+        <v>-1.671284161922326</v>
       </c>
       <c r="D158" t="n">
         <v>0.7986401324346124</v>
       </c>
       <c r="E158" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F158" t="n">
         <v>-0.8657371928209737</v>
@@ -7399,7 +7399,7 @@
         <v>-0.5187442006946303</v>
       </c>
       <c r="L158" t="n">
-        <v>-0.9368993718770108</v>
+        <v>-0.9168831095825996</v>
       </c>
       <c r="M158" t="n">
         <v>-1.406938496100678</v>
@@ -7410,13 +7410,13 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>1.282940959293063</v>
+        <v>1.339061469925893</v>
       </c>
       <c r="B159" t="n">
-        <v>0.8067748883961599</v>
+        <v>1.583862102492648</v>
       </c>
       <c r="C159" t="n">
-        <v>0.1612707914997614</v>
+        <v>-1.671284161922326</v>
       </c>
       <c r="D159" t="n">
         <v>0.7986401324346124</v>
@@ -7443,7 +7443,7 @@
         <v>-0.8686205205815232</v>
       </c>
       <c r="L159" t="n">
-        <v>-0.5204037830178967</v>
+        <v>-0.5092865229811483</v>
       </c>
       <c r="M159" t="n">
         <v>-1.406938496100678</v>
@@ -7454,19 +7454,19 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>1.282940959293063</v>
+        <v>1.339061469925893</v>
       </c>
       <c r="B160" t="n">
-        <v>0.8067748883961599</v>
+        <v>1.583862102492648</v>
       </c>
       <c r="C160" t="n">
-        <v>0.1612707914997614</v>
+        <v>-1.671284161922326</v>
       </c>
       <c r="D160" t="n">
         <v>0.7986401324346124</v>
       </c>
       <c r="E160" t="n">
-        <v>0.3016562502268909</v>
+        <v>0.3016562502268911</v>
       </c>
       <c r="F160" t="n">
         <v>-0.730719448544361</v>
@@ -7487,7 +7487,7 @@
         <v>1.697139158589025</v>
       </c>
       <c r="L160" t="n">
-        <v>-0.4236820585908986</v>
+        <v>-0.4146313914955032</v>
       </c>
       <c r="M160" t="n">
         <v>-1.406938496100678</v>
@@ -7498,19 +7498,19 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>1.282940959293063</v>
+        <v>1.339061469925893</v>
       </c>
       <c r="B161" t="n">
-        <v>0.8067748883961599</v>
+        <v>1.583862102492648</v>
       </c>
       <c r="C161" t="n">
-        <v>0.1612707914997614</v>
+        <v>-1.671284161922326</v>
       </c>
       <c r="D161" t="n">
         <v>-1.20517484870554</v>
       </c>
       <c r="E161" t="n">
-        <v>-0.8317401748482529</v>
+        <v>-0.831740174848253</v>
       </c>
       <c r="F161" t="n">
         <v>-0.937672876247038</v>
@@ -7531,7 +7531,7 @@
         <v>1.230637398739834</v>
       </c>
       <c r="L161" t="n">
-        <v>-0.9368993718770108</v>
+        <v>-0.9168831095825996</v>
       </c>
       <c r="M161" t="n">
         <v>1.055556285591372</v>
@@ -7542,19 +7542,19 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>1.795702842624089</v>
+        <v>2.002756236933897</v>
       </c>
       <c r="B162" t="n">
-        <v>1.02244056508347</v>
+        <v>-1.356243650857806</v>
       </c>
       <c r="C162" t="n">
-        <v>0.1048698298176612</v>
+        <v>-1.835522640849212</v>
       </c>
       <c r="D162" t="n">
         <v>-0.5372365216588224</v>
       </c>
       <c r="E162" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F162" t="n">
         <v>-1.167313711799473</v>
@@ -7575,7 +7575,7 @@
         <v>-0.8686205205815232</v>
       </c>
       <c r="L162" t="n">
-        <v>-1.122039488682346e-16</v>
+        <v>-1.563055075542878</v>
       </c>
       <c r="M162" t="n">
         <v>0.7037713167782218</v>
@@ -7586,19 +7586,19 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>1.795702842624089</v>
+        <v>2.002756236933897</v>
       </c>
       <c r="B163" t="n">
-        <v>1.02244056508347</v>
+        <v>-1.356243650857806</v>
       </c>
       <c r="C163" t="n">
-        <v>0.1048698298176612</v>
+        <v>-1.835522640849212</v>
       </c>
       <c r="D163" t="n">
         <v>-0.5372365216588224</v>
       </c>
       <c r="E163" t="n">
-        <v>0.6794550585852722</v>
+        <v>0.6794550585852724</v>
       </c>
       <c r="F163" t="n">
         <v>-0.7024985265849051</v>
@@ -7619,7 +7619,7 @@
         <v>-0.7519950806192256</v>
       </c>
       <c r="L163" t="n">
-        <v>0.0303178723929698</v>
+        <v>0.0296682052738511</v>
       </c>
       <c r="M163" t="n">
         <v>-0.7033685584743783</v>
@@ -7630,19 +7630,19 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>1.795702842624089</v>
+        <v>2.002756236933897</v>
       </c>
       <c r="B164" t="n">
-        <v>-0.3808881835002534</v>
+        <v>0.7484665367130705</v>
       </c>
       <c r="C164" t="n">
-        <v>0.1048698298176612</v>
+        <v>-1.835522640849212</v>
       </c>
       <c r="D164" t="n">
         <v>-0.5372365216588224</v>
       </c>
       <c r="E164" t="n">
-        <v>-0.8317401748482529</v>
+        <v>-0.831740174848253</v>
       </c>
       <c r="F164" t="n">
         <v>-1.125812355976744</v>
@@ -7663,7 +7663,7 @@
         <v>1.46388827866443</v>
       </c>
       <c r="L164" t="n">
-        <v>-0.9368993718770108</v>
+        <v>-0.9168831095825996</v>
       </c>
       <c r="M164" t="n">
         <v>-1.406938496100678</v>
@@ -7674,19 +7674,19 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>1.795702842624089</v>
+        <v>2.002756236933897</v>
       </c>
       <c r="B165" t="n">
-        <v>1.02244056508347</v>
+        <v>-1.356243650857806</v>
       </c>
       <c r="C165" t="n">
-        <v>0.1048698298176612</v>
+        <v>-1.835522640849212</v>
       </c>
       <c r="D165" t="n">
         <v>-0.5372365216588224</v>
       </c>
       <c r="E165" t="n">
-        <v>0.6794550585852722</v>
+        <v>0.6794550585852724</v>
       </c>
       <c r="F165" t="n">
         <v>-0.6277960861039923</v>
@@ -7698,7 +7698,7 @@
         <v>1.420544475949613e-16</v>
       </c>
       <c r="I165" t="n">
-        <v>48.65173679263987</v>
+        <v>55.22454007768361</v>
       </c>
       <c r="J165" t="n">
         <v>1.372818258176657</v>
@@ -7707,7 +7707,7 @@
         <v>-0.6353696406569279</v>
       </c>
       <c r="L165" t="n">
-        <v>0.0007091812418479</v>
+        <v>0.0006921446149801001</v>
       </c>
       <c r="M165" t="n">
         <v>0.7037713167782218</v>
@@ -7718,13 +7718,13 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>1.795702842624089</v>
+        <v>2.002756236933897</v>
       </c>
       <c r="B166" t="n">
-        <v>1.02244056508347</v>
+        <v>-1.356243650857806</v>
       </c>
       <c r="C166" t="n">
-        <v>0.1048698298176612</v>
+        <v>-1.835522640849212</v>
       </c>
       <c r="D166" t="n">
         <v>-0.5372365216588224</v>
@@ -7751,7 +7751,7 @@
         <v>1.230637398739834</v>
       </c>
       <c r="L166" t="n">
-        <v>-0.9368993718770108</v>
+        <v>-0.9168831095825996</v>
       </c>
       <c r="M166" t="n">
         <v>1.055556285591372</v>
@@ -7762,19 +7762,19 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>1.795702842624089</v>
+        <v>2.002756236933897</v>
       </c>
       <c r="B167" t="n">
-        <v>1.02244056508347</v>
+        <v>-1.356243650857806</v>
       </c>
       <c r="C167" t="n">
-        <v>0.1048698298176612</v>
+        <v>-1.835522640849212</v>
       </c>
       <c r="D167" t="n">
         <v>-0.5372365216588224</v>
       </c>
       <c r="E167" t="n">
-        <v>1.812851483660416</v>
+        <v>1.812851483660417</v>
       </c>
       <c r="F167" t="n">
         <v>-0.3151525389060982</v>
@@ -7795,7 +7795,7 @@
         <v>1.580513718626727</v>
       </c>
       <c r="L167" t="n">
-        <v>0.050056999827051</v>
+        <v>0.0489855790464317</v>
       </c>
       <c r="M167" t="n">
         <v>0.7037713167782218</v>
@@ -7806,19 +7806,19 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>1.795702842624089</v>
+        <v>2.002756236933897</v>
       </c>
       <c r="B168" t="n">
-        <v>1.02244056508347</v>
+        <v>-1.356243650857806</v>
       </c>
       <c r="C168" t="n">
-        <v>0.1048698298176612</v>
+        <v>-1.835522640849212</v>
       </c>
       <c r="D168" t="n">
         <v>-0.5372365216588224</v>
       </c>
       <c r="E168" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F168" t="n">
         <v>-0.5221059666087751</v>
@@ -7839,7 +7839,7 @@
         <v>-0.8686205205815232</v>
       </c>
       <c r="L168" t="n">
-        <v>-1.167847162855761</v>
+        <v>-1.142896382721793</v>
       </c>
       <c r="M168" t="n">
         <v>-1.406938496100678</v>
@@ -7850,13 +7850,13 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>1.795702842624089</v>
+        <v>2.002756236933897</v>
       </c>
       <c r="B169" t="n">
-        <v>1.02244056508347</v>
+        <v>-1.356243650857806</v>
       </c>
       <c r="C169" t="n">
-        <v>0.1048698298176612</v>
+        <v>-1.835522640849212</v>
       </c>
       <c r="D169" t="n">
         <v>-0.5372365216588224</v>
@@ -7883,7 +7883,7 @@
         <v>1.697139158589025</v>
       </c>
       <c r="L169" t="n">
-        <v>0.3954917299234727</v>
+        <v>0.3870396200665927</v>
       </c>
       <c r="M169" t="n">
         <v>0.7037713167782218</v>
@@ -7894,19 +7894,19 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>1.795702842624089</v>
+        <v>2.002756236933897</v>
       </c>
       <c r="B170" t="n">
-        <v>1.02244056508347</v>
+        <v>-1.356243650857806</v>
       </c>
       <c r="C170" t="n">
-        <v>0.1048698298176612</v>
+        <v>-1.835522640849212</v>
       </c>
       <c r="D170" t="n">
         <v>-0.5372365216588224</v>
       </c>
       <c r="E170" t="n">
-        <v>-0.8317401748482529</v>
+        <v>-0.831740174848253</v>
       </c>
       <c r="F170" t="n">
         <v>0.6725797296748594</v>
@@ -7918,7 +7918,7 @@
         <v>1.420544475949613e-16</v>
       </c>
       <c r="I170" t="n">
-        <v>49.03194021180714</v>
+        <v>49.36058037605932</v>
       </c>
       <c r="J170" t="n">
         <v>-1.095682162976588</v>
@@ -7927,7 +7927,7 @@
         <v>1.46388827866443</v>
       </c>
       <c r="L170" t="n">
-        <v>-0.9368993718770108</v>
+        <v>-0.9168831095825996</v>
       </c>
       <c r="M170" t="n">
         <v>0.7037713167782218</v>
@@ -7938,19 +7938,19 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B171" t="n">
-        <v>-1.315639695827425</v>
+        <v>0.090925644091836</v>
       </c>
       <c r="C171" t="n">
-        <v>-0.5719417103675415</v>
+        <v>0.2448314255580015</v>
       </c>
       <c r="D171" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E171" t="n">
-        <v>0.6794550585852722</v>
+        <v>0.6794550585852724</v>
       </c>
       <c r="F171" t="n">
         <v>0.3710032106963596</v>
@@ -7971,7 +7971,7 @@
         <v>-2.071683979250907e-16</v>
       </c>
       <c r="L171" t="n">
-        <v>1.658795885704672</v>
+        <v>1.623351541511753</v>
       </c>
       <c r="M171" t="n">
         <v>-1.758723464913828</v>
@@ -7982,19 +7982,19 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B172" t="n">
-        <v>-1.315639695827425</v>
+        <v>0.090925644091836</v>
       </c>
       <c r="C172" t="n">
-        <v>-0.5719417103675415</v>
+        <v>0.2448314255580015</v>
       </c>
       <c r="D172" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E172" t="n">
-        <v>0.3016562502268909</v>
+        <v>0.3016562502268911</v>
       </c>
       <c r="F172" t="n">
         <v>0.1441291321987728</v>
@@ -8015,7 +8015,7 @@
         <v>-0.7519950806192256</v>
       </c>
       <c r="L172" t="n">
-        <v>0.6817090777176507</v>
+        <v>0.6671415397690118</v>
       </c>
       <c r="M172" t="n">
         <v>0.7037713167782218</v>
@@ -8026,13 +8026,13 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B173" t="n">
-        <v>-1.315639695827425</v>
+        <v>0.090925644091836</v>
       </c>
       <c r="C173" t="n">
-        <v>-0.5719417103675415</v>
+        <v>0.2448314255580015</v>
       </c>
       <c r="D173" t="n">
         <v>0.130701805387895</v>
@@ -8059,7 +8059,7 @@
         <v>1.230637398739834</v>
       </c>
       <c r="L173" t="n">
-        <v>-0.9368993718770108</v>
+        <v>-0.9168831095825996</v>
       </c>
       <c r="M173" t="n">
         <v>0.7037713167782218</v>
@@ -8070,13 +8070,13 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B174" t="n">
-        <v>-1.315639695827425</v>
+        <v>0.090925644091836</v>
       </c>
       <c r="C174" t="n">
-        <v>-0.5719417103675415</v>
+        <v>0.2448314255580015</v>
       </c>
       <c r="D174" t="n">
         <v>0.130701805387895</v>
@@ -8103,7 +8103,7 @@
         <v>1.230637398739834</v>
       </c>
       <c r="L174" t="n">
-        <v>0.6817090777176507</v>
+        <v>0.6671415397690118</v>
       </c>
       <c r="M174" t="n">
         <v>-0.3515835896612282</v>
@@ -8114,19 +8114,19 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B175" t="n">
-        <v>-1.315639695827425</v>
+        <v>0.090925644091836</v>
       </c>
       <c r="C175" t="n">
-        <v>-0.5719417103675415</v>
+        <v>0.2448314255580015</v>
       </c>
       <c r="D175" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E175" t="n">
-        <v>0.3016562502268909</v>
+        <v>0.3016562502268911</v>
       </c>
       <c r="F175" t="n">
         <v>1.355968722222469</v>
@@ -8147,7 +8147,7 @@
         <v>-0.4021187607323326</v>
       </c>
       <c r="L175" t="n">
-        <v>1.323230719325291</v>
+        <v>1.294956187377882</v>
       </c>
       <c r="M175" t="n">
         <v>0.7037713167782218</v>
@@ -8158,19 +8158,19 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B176" t="n">
-        <v>-1.315639695827425</v>
+        <v>0.090925644091836</v>
       </c>
       <c r="C176" t="n">
-        <v>-0.5719417103675415</v>
+        <v>0.2448314255580015</v>
       </c>
       <c r="D176" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E176" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F176" t="n">
         <v>-0.5198925609648961</v>
@@ -8191,7 +8191,7 @@
         <v>-0.4021187607323326</v>
       </c>
       <c r="L176" t="n">
-        <v>0.5336656219620414</v>
+        <v>0.5222612364746571</v>
       </c>
       <c r="M176" t="n">
         <v>1.055556285591372</v>
@@ -8202,19 +8202,19 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B177" t="n">
-        <v>-1.315639695827425</v>
+        <v>0.090925644091836</v>
       </c>
       <c r="C177" t="n">
-        <v>-0.5719417103675415</v>
+        <v>0.2448314255580015</v>
       </c>
       <c r="D177" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E177" t="n">
-        <v>-0.8317401748482529</v>
+        <v>-0.831740174848253</v>
       </c>
       <c r="F177" t="n">
         <v>-0.5198925609648961</v>
@@ -8235,7 +8235,7 @@
         <v>-0.9852459605438209</v>
       </c>
       <c r="L177" t="n">
-        <v>-0.9368993718770108</v>
+        <v>-0.9168831095825996</v>
       </c>
       <c r="M177" t="n">
         <v>0.7037713167782218</v>
@@ -8246,19 +8246,19 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>-0.2553446907000148</v>
+        <v>-2.947396846622059e-16</v>
       </c>
       <c r="B178" t="n">
-        <v>-1.315639695827425</v>
+        <v>0.090925644091836</v>
       </c>
       <c r="C178" t="n">
-        <v>-0.5719417103675415</v>
+        <v>0.2448314255580015</v>
       </c>
       <c r="D178" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E178" t="n">
-        <v>0.6794550585852722</v>
+        <v>0.6794550585852724</v>
       </c>
       <c r="F178" t="n">
         <v>0.7943170400881986</v>
@@ -8279,7 +8279,7 @@
         <v>-0.7519950806192256</v>
       </c>
       <c r="L178" t="n">
-        <v>0.5336656219620414</v>
+        <v>0.5222612364746571</v>
       </c>
       <c r="M178" t="n">
         <v>-1.758723464913828</v>
@@ -8290,13 +8290,13 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B179" t="n">
-        <v>-1.315639695827425</v>
+        <v>0.090925644091836</v>
       </c>
       <c r="C179" t="n">
-        <v>-0.5719417103675415</v>
+        <v>0.2448314255580015</v>
       </c>
       <c r="D179" t="n">
         <v>0.130701805387895</v>
@@ -8323,7 +8323,7 @@
         <v>-0.285493320770035</v>
       </c>
       <c r="L179" t="n">
-        <v>-0.1473342745137612</v>
+        <v>-0.1441881586793745</v>
       </c>
       <c r="M179" t="n">
         <v>-0.3515835896612282</v>
@@ -8334,13 +8334,13 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B180" t="n">
-        <v>-1.315639695827425</v>
+        <v>0.090925644091836</v>
       </c>
       <c r="C180" t="n">
-        <v>-0.5719417103675415</v>
+        <v>0.2448314255580015</v>
       </c>
       <c r="D180" t="n">
         <v>0.130701805387895</v>
@@ -8367,7 +8367,7 @@
         <v>1.347262838702132</v>
       </c>
       <c r="L180" t="n">
-        <v>0.5336656219620414</v>
+        <v>0.5222612364746571</v>
       </c>
       <c r="M180" t="n">
         <v>0.7037713167782218</v>
@@ -8378,19 +8378,19 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B181" t="n">
-        <v>-1.315639695827425</v>
+        <v>0.090925644091836</v>
       </c>
       <c r="C181" t="n">
-        <v>-0.5719417103675415</v>
+        <v>0.2448314255580015</v>
       </c>
       <c r="D181" t="n">
         <v>-1.20517484870554</v>
       </c>
       <c r="E181" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F181" t="n">
         <v>-2.516350882477691e-16</v>
@@ -8411,7 +8411,7 @@
         <v>1.230637398739834</v>
       </c>
       <c r="L181" t="n">
-        <v>1.866056723762525</v>
+        <v>1.826183966123849</v>
       </c>
       <c r="M181" t="n">
         <v>-0.7033685584743783</v>
@@ -8422,19 +8422,19 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B182" t="n">
-        <v>-1.315639695827425</v>
+        <v>0.090925644091836</v>
       </c>
       <c r="C182" t="n">
-        <v>-0.5719417103675415</v>
+        <v>0.2448314255580015</v>
       </c>
       <c r="D182" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E182" t="n">
-        <v>2.190650292018797</v>
+        <v>2.190650292018798</v>
       </c>
       <c r="F182" t="n">
         <v>3.400602185755599</v>
@@ -8455,7 +8455,7 @@
         <v>1.230637398739834</v>
       </c>
       <c r="L182" t="n">
-        <v>0.5336656219620414</v>
+        <v>0.5222612364746571</v>
       </c>
       <c r="M182" t="n">
         <v>0.7037713167782218</v>
@@ -8466,13 +8466,13 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B183" t="n">
-        <v>-1.315639695827425</v>
+        <v>0.090925644091836</v>
       </c>
       <c r="C183" t="n">
-        <v>-0.5719417103675415</v>
+        <v>0.2448314255580015</v>
       </c>
       <c r="D183" t="n">
         <v>0.130701805387895</v>
@@ -8499,7 +8499,7 @@
         <v>-0.4021187607323326</v>
       </c>
       <c r="L183" t="n">
-        <v>1.323230719325291</v>
+        <v>1.294956187377882</v>
       </c>
       <c r="M183" t="n">
         <v>0.7037713167782218</v>
@@ -8510,19 +8510,19 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>-0.2553446907000148</v>
+        <v>-2.947396846622059e-16</v>
       </c>
       <c r="B184" t="n">
-        <v>-1.315639695827425</v>
+        <v>0.090925644091836</v>
       </c>
       <c r="C184" t="n">
-        <v>-0.5719417103675415</v>
+        <v>0.2448314255580015</v>
       </c>
       <c r="D184" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E184" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F184" t="n">
         <v>-0.4645574198679237</v>
@@ -8543,7 +8543,7 @@
         <v>-0.4021187607323326</v>
       </c>
       <c r="L184" t="n">
-        <v>0.336274347621229</v>
+        <v>0.3290874987488508</v>
       </c>
       <c r="M184" t="n">
         <v>-1.758723464913828</v>
@@ -8554,19 +8554,19 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B185" t="n">
-        <v>-1.315639695827425</v>
+        <v>0.090925644091836</v>
       </c>
       <c r="C185" t="n">
-        <v>-0.5719417103675415</v>
+        <v>0.2448314255580015</v>
       </c>
       <c r="D185" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E185" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F185" t="n">
         <v>-0.0523106186954792</v>
@@ -8578,7 +8578,7 @@
         <v>-0.4016515137931061</v>
       </c>
       <c r="I185" t="n">
-        <v>48.65144758869703</v>
+        <v>41.52166666666667</v>
       </c>
       <c r="J185" t="n">
         <v>-0.10828199451529</v>
@@ -8587,7 +8587,7 @@
         <v>-0.4021187607323326</v>
       </c>
       <c r="L185" t="n">
-        <v>-0.7395080975361984</v>
+        <v>-0.7237093718567933</v>
       </c>
       <c r="M185" t="n">
         <v>0.7037713167782218</v>
@@ -8598,19 +8598,19 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B186" t="n">
-        <v>-1.315639695827425</v>
+        <v>0.090925644091836</v>
       </c>
       <c r="C186" t="n">
-        <v>-0.5719417103675415</v>
+        <v>0.2448314255580015</v>
       </c>
       <c r="D186" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E186" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F186" t="n">
         <v>0.0030245224014931</v>
@@ -8631,7 +8631,7 @@
         <v>1.580513718626727</v>
       </c>
       <c r="L186" t="n">
-        <v>-0.9368993718770108</v>
+        <v>-0.9168831095825996</v>
       </c>
       <c r="M186" t="n">
         <v>1.055556285591372</v>
@@ -8642,13 +8642,13 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B187" t="n">
-        <v>-1.315639695827425</v>
+        <v>0.090925644091836</v>
       </c>
       <c r="C187" t="n">
-        <v>-0.5719417103675415</v>
+        <v>0.2448314255580015</v>
       </c>
       <c r="D187" t="n">
         <v>0.130701805387895</v>
@@ -8675,7 +8675,7 @@
         <v>1.46388827866443</v>
       </c>
       <c r="L187" t="n">
-        <v>1.323230719325291</v>
+        <v>1.294956187377882</v>
       </c>
       <c r="M187" t="n">
         <v>0.7037713167782218</v>
@@ -8686,19 +8686,19 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B188" t="n">
-        <v>-1.315639695827425</v>
+        <v>0.090925644091836</v>
       </c>
       <c r="C188" t="n">
-        <v>-1.023149403824343</v>
+        <v>-0.0836455322957689</v>
       </c>
       <c r="D188" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E188" t="n">
-        <v>-0.8317401748482529</v>
+        <v>-0.831740174848253</v>
       </c>
       <c r="F188" t="n">
         <v>-0.9321393621373406</v>
@@ -8719,7 +8719,7 @@
         <v>1.114011958777537</v>
       </c>
       <c r="L188" t="n">
-        <v>-0.9368993718770108</v>
+        <v>-0.9168831095825996</v>
       </c>
       <c r="M188" t="n">
         <v>0.7037713167782218</v>
@@ -8730,19 +8730,19 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B189" t="n">
-        <v>-1.315639695827425</v>
+        <v>0.090925644091836</v>
       </c>
       <c r="C189" t="n">
-        <v>-0.5719417103675415</v>
+        <v>0.2448314255580015</v>
       </c>
       <c r="D189" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E189" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F189" t="n">
         <v>-0.5447933744585337</v>
@@ -8763,7 +8763,7 @@
         <v>-0.4021187607323326</v>
       </c>
       <c r="L189" t="n">
-        <v>-0.9368993718770108</v>
+        <v>-0.9168831095825996</v>
       </c>
       <c r="M189" t="n">
         <v>1.055556285591372</v>
@@ -8774,13 +8774,13 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B190" t="n">
-        <v>-1.315639695827425</v>
+        <v>0.090925644091836</v>
       </c>
       <c r="C190" t="n">
-        <v>-0.5719417103675415</v>
+        <v>0.2448314255580015</v>
       </c>
       <c r="D190" t="n">
         <v>0.130701805387895</v>
@@ -8807,7 +8807,7 @@
         <v>-0.8686205205815232</v>
       </c>
       <c r="L190" t="n">
-        <v>0.1487526369974572</v>
+        <v>0.1455724479093348</v>
       </c>
       <c r="M190" t="n">
         <v>0.7037713167782218</v>
@@ -8818,19 +8818,19 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B191" t="n">
-        <v>-1.315639695827425</v>
+        <v>0.090925644091836</v>
       </c>
       <c r="C191" t="n">
-        <v>-0.5719417103675415</v>
+        <v>0.2448314255580015</v>
       </c>
       <c r="D191" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E191" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F191" t="n">
         <v>-0.3262195671254927</v>
@@ -8851,7 +8851,7 @@
         <v>-0.4021187607323326</v>
       </c>
       <c r="L191" t="n">
-        <v>-0.1572038382308019</v>
+        <v>-0.1538468455656648</v>
       </c>
       <c r="M191" t="n">
         <v>0.7037713167782218</v>
@@ -8862,19 +8862,19 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B192" t="n">
-        <v>-1.315639695827425</v>
+        <v>0.090925644091836</v>
       </c>
       <c r="C192" t="n">
-        <v>-0.5719417103675415</v>
+        <v>0.2448314255580015</v>
       </c>
       <c r="D192" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E192" t="n">
-        <v>0.3016562502268909</v>
+        <v>0.3016562502268911</v>
       </c>
       <c r="F192" t="n">
         <v>0.4595394364515155</v>
@@ -8895,7 +8895,7 @@
         <v>1.46388827866443</v>
       </c>
       <c r="L192" t="n">
-        <v>1.076491626399275</v>
+        <v>1.053489015220624</v>
       </c>
       <c r="M192" t="n">
         <v>1.055556285591372</v>
@@ -8906,13 +8906,13 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B193" t="n">
-        <v>-1.315639695827425</v>
+        <v>0.090925644091836</v>
       </c>
       <c r="C193" t="n">
-        <v>-0.5719417103675415</v>
+        <v>0.2448314255580015</v>
       </c>
       <c r="D193" t="n">
         <v>0.130701805387895</v>
@@ -8939,7 +8939,7 @@
         <v>-0.8686205205815232</v>
       </c>
       <c r="L193" t="n">
-        <v>0.336274347621229</v>
+        <v>0.3290874987488508</v>
       </c>
       <c r="M193" t="n">
         <v>0.7037713167782218</v>
@@ -8950,19 +8950,19 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B194" t="n">
-        <v>-1.315639695827425</v>
+        <v>0.090925644091836</v>
       </c>
       <c r="C194" t="n">
-        <v>-0.5719417103675415</v>
+        <v>0.2448314255580015</v>
       </c>
       <c r="D194" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E194" t="n">
-        <v>-0.8317401748482529</v>
+        <v>-0.831740174848253</v>
       </c>
       <c r="F194" t="n">
         <v>-0.7965682664497582</v>
@@ -8983,7 +8983,7 @@
         <v>-0.6353696406569279</v>
       </c>
       <c r="L194" t="n">
-        <v>-0.9368993718770108</v>
+        <v>-0.9168831095825996</v>
       </c>
       <c r="M194" t="n">
         <v>0.7037713167782218</v>
@@ -8994,19 +8994,19 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B195" t="n">
-        <v>-1.315639695827425</v>
+        <v>0.090925644091836</v>
       </c>
       <c r="C195" t="n">
-        <v>-0.5719417103675415</v>
+        <v>0.2448314255580015</v>
       </c>
       <c r="D195" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E195" t="n">
-        <v>3.701845525452323</v>
+        <v>3.701845525452324</v>
       </c>
       <c r="F195" t="n">
         <v>4.036956308370781</v>
@@ -9018,7 +9018,7 @@
         <v>0.8778612007168733</v>
       </c>
       <c r="I195" t="n">
-        <v>48.65120300356686</v>
+        <v>38.68691666666667</v>
       </c>
       <c r="J195" t="n">
         <v>-1.095682162976588</v>
@@ -9027,7 +9027,7 @@
         <v>1.230637398739834</v>
       </c>
       <c r="L195" t="n">
-        <v>1.520621993666103</v>
+        <v>1.488129925103688</v>
       </c>
       <c r="M195" t="n">
         <v>0.7037713167782218</v>
@@ -9038,19 +9038,19 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B196" t="n">
-        <v>-1.315639695827425</v>
+        <v>0.090925644091836</v>
       </c>
       <c r="C196" t="n">
-        <v>-0.5719417103675415</v>
+        <v>0.2448314255580015</v>
       </c>
       <c r="D196" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E196" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F196" t="n">
         <v>-0.2847182113027633</v>
@@ -9071,7 +9071,7 @@
         <v>-0.7519950806192256</v>
       </c>
       <c r="L196" t="n">
-        <v>-0.3052472939864111</v>
+        <v>-0.2987271488600195</v>
       </c>
       <c r="M196" t="n">
         <v>1.055556285591372</v>
@@ -9082,19 +9082,19 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B197" t="n">
-        <v>-1.315639695827425</v>
+        <v>0.090925644091836</v>
       </c>
       <c r="C197" t="n">
-        <v>-0.5719417103675415</v>
+        <v>0.2448314255580015</v>
       </c>
       <c r="D197" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E197" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F197" t="n">
         <v>0.0583596634984655</v>
@@ -9115,7 +9115,7 @@
         <v>-0.7519950806192256</v>
       </c>
       <c r="L197" t="n">
-        <v>-0.7395080975361984</v>
+        <v>-0.7237093718567933</v>
       </c>
       <c r="M197" t="n">
         <v>1.055556285591372</v>
@@ -9126,19 +9126,19 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B198" t="n">
-        <v>-1.315639695827425</v>
+        <v>0.090925644091836</v>
       </c>
       <c r="C198" t="n">
-        <v>-0.5719417103675415</v>
+        <v>0.2448314255580015</v>
       </c>
       <c r="D198" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E198" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F198" t="n">
         <v>-0.6305628431588409</v>
@@ -9159,7 +9159,7 @@
         <v>1.580513718626727</v>
       </c>
       <c r="L198" t="n">
-        <v>1.323230719325291</v>
+        <v>1.294956187377882</v>
       </c>
       <c r="M198" t="n">
         <v>-0.7033685584743783</v>
@@ -9170,19 +9170,19 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B199" t="n">
-        <v>-1.315639695827425</v>
+        <v>0.090925644091836</v>
       </c>
       <c r="C199" t="n">
-        <v>-0.5719417103675415</v>
+        <v>0.2448314255580015</v>
       </c>
       <c r="D199" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E199" t="n">
-        <v>-0.4539413664898716</v>
+        <v>-0.4539413664898717</v>
       </c>
       <c r="F199" t="n">
         <v>-0.3538871376739789</v>
@@ -9203,7 +9203,7 @@
         <v>-0.4021187607323326</v>
       </c>
       <c r="L199" t="n">
-        <v>0.7310568963028538</v>
+        <v>0.7154349742004633</v>
       </c>
       <c r="M199" t="n">
         <v>-0.7033685584743783</v>
@@ -9214,19 +9214,19 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B200" t="n">
-        <v>-1.315639695827425</v>
+        <v>0.090925644091836</v>
       </c>
       <c r="C200" t="n">
-        <v>-1.023149403824343</v>
+        <v>-0.0836455322957689</v>
       </c>
       <c r="D200" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E200" t="n">
-        <v>-0.8317401748482529</v>
+        <v>-0.831740174848253</v>
       </c>
       <c r="F200" t="n">
         <v>-0.7965682664497582</v>
@@ -9247,7 +9247,7 @@
         <v>-0.4021187607323326</v>
       </c>
       <c r="L200" t="n">
-        <v>-0.9368993718770108</v>
+        <v>-0.9168831095825996</v>
       </c>
       <c r="M200" t="n">
         <v>1.055556285591372</v>
@@ -9258,19 +9258,19 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>0.7701790759620369</v>
+        <v>0.6753667029178887</v>
       </c>
       <c r="B201" t="n">
-        <v>-1.315639695827425</v>
+        <v>0.090925644091836</v>
       </c>
       <c r="C201" t="n">
-        <v>-0.5719417103675415</v>
+        <v>0.2448314255580015</v>
       </c>
       <c r="D201" t="n">
         <v>0.130701805387895</v>
       </c>
       <c r="E201" t="n">
-        <v>-0.8317401748482529</v>
+        <v>-0.831740174848253</v>
       </c>
       <c r="F201" t="n">
         <v>-0.7965682664497582</v>
@@ -9291,7 +9291,7 @@
         <v>1.230637398739834</v>
       </c>
       <c r="L201" t="n">
-        <v>-0.9368993718770108</v>
+        <v>-0.9168831095825996</v>
       </c>
       <c r="M201" t="n">
         <v>0.7037713167782218</v>
